--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130298671</v>
+        <v>130300998</v>
       </c>
       <c r="B2" t="n">
         <v>98920</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490825</v>
+        <v>490659</v>
       </c>
       <c r="R2" t="n">
-        <v>6687809</v>
+        <v>6687865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130299512</v>
+        <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490708</v>
+        <v>490628</v>
       </c>
       <c r="R3" t="n">
-        <v>6687780</v>
+        <v>6687894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300998</v>
+        <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490659</v>
+        <v>490708</v>
       </c>
       <c r="R5" t="n">
-        <v>6687865</v>
+        <v>6687780</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300930</v>
+        <v>130298671</v>
       </c>
       <c r="B6" t="n">
         <v>98920</v>
@@ -1144,14 +1144,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490628</v>
+        <v>490825</v>
       </c>
       <c r="R6" t="n">
-        <v>6687894</v>
+        <v>6687809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B8" t="n">
         <v>98920</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B9" t="n">
         <v>98920</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R9" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130300768</v>
+        <v>130299757</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490629</v>
+        <v>490654</v>
       </c>
       <c r="R13" t="n">
-        <v>6687910</v>
+        <v>6687872</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298782</v>
+        <v>130298405</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -2002,31 +2002,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490803</v>
+        <v>490825</v>
       </c>
       <c r="R14" t="n">
-        <v>6687883</v>
+        <v>6687878</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B15" t="n">
         <v>98920</v>
@@ -2123,17 +2109,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R15" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,45 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130299757</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490654</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687872</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2272,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,12 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,32 +2314,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130298439</v>
+        <v>130299411</v>
       </c>
       <c r="B17" t="n">
-        <v>92026</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490826</v>
+        <v>490679</v>
       </c>
       <c r="R17" t="n">
-        <v>6687871</v>
+        <v>6687837</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130299411</v>
+        <v>130298439</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>92026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490679</v>
+        <v>490826</v>
       </c>
       <c r="R18" t="n">
-        <v>6687837</v>
+        <v>6687871</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2528,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298529</v>
+        <v>130299218</v>
       </c>
       <c r="B19" t="n">
         <v>98920</v>
@@ -2556,31 +2556,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490885</v>
+        <v>490666</v>
       </c>
       <c r="R19" t="n">
-        <v>6687821</v>
+        <v>6687855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2612,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298375</v>
+        <v>130298529</v>
       </c>
       <c r="B20" t="n">
         <v>98920</v>
@@ -2679,17 +2665,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2698,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490816</v>
+        <v>490885</v>
       </c>
       <c r="R20" t="n">
-        <v>6687911</v>
+        <v>6687821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2733,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,7 +2756,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130299218</v>
+        <v>130298375</v>
       </c>
       <c r="B21" t="n">
         <v>98920</v>
@@ -2798,17 +2784,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490666</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6687855</v>
+        <v>6687911</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130299399</v>
+        <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>81165</v>
+        <v>97166</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490680</v>
+        <v>490743</v>
       </c>
       <c r="R26" t="n">
-        <v>6687839</v>
+        <v>6687908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130300054</v>
+        <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>97166</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490743</v>
+        <v>490831</v>
       </c>
       <c r="R27" t="n">
-        <v>6687908</v>
+        <v>6687885</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B28" t="n">
-        <v>91728</v>
+        <v>81165</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R28" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130299013</v>
+        <v>130298471</v>
       </c>
       <c r="B29" t="n">
         <v>98920</v>
@@ -3679,31 +3679,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490722</v>
+        <v>490854</v>
       </c>
       <c r="R29" t="n">
-        <v>6687888</v>
+        <v>6687846</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3735,7 +3721,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3745,12 +3731,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,50 +3758,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300987</v>
+        <v>130299120</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490657</v>
+        <v>490690</v>
       </c>
       <c r="R30" t="n">
-        <v>6687863</v>
+        <v>6687921</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3852,7 +3828,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3862,7 +3838,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,7 +3865,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130299915</v>
       </c>
       <c r="B31" t="n">
         <v>98920</v>
@@ -3924,10 +3900,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490724</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687908</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3959,7 +3935,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,7 +3945,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3996,7 +3972,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299120</v>
+        <v>130299013</v>
       </c>
       <c r="B32" t="n">
         <v>98920</v>
@@ -4024,17 +4000,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490690</v>
+        <v>490722</v>
       </c>
       <c r="R32" t="n">
-        <v>6687921</v>
+        <v>6687888</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4066,7 +4056,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4076,7 +4066,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4103,7 +4098,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299432</v>
+        <v>130300987</v>
       </c>
       <c r="B33" t="n">
         <v>57823</v>
@@ -4134,7 +4129,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490697</v>
+        <v>490657</v>
       </c>
       <c r="R33" t="n">
-        <v>6687828</v>
+        <v>6687863</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4178,7 +4173,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4188,7 +4183,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4215,45 +4210,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299915</v>
+        <v>130300532</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490724</v>
+        <v>490688</v>
       </c>
       <c r="R34" t="n">
-        <v>6687908</v>
+        <v>6687940</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4295,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,38 +4327,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300532</v>
+        <v>130299432</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4367,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490688</v>
+        <v>490697</v>
       </c>
       <c r="R35" t="n">
-        <v>6687940</v>
+        <v>6687828</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4402,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4412,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130300089</v>
       </c>
       <c r="B37" t="n">
         <v>97166</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490754</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687921</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299645</v>
+        <v>130300601</v>
       </c>
       <c r="B38" t="n">
         <v>98920</v>
@@ -4684,14 +4684,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490670</v>
+        <v>490648</v>
       </c>
       <c r="R38" t="n">
-        <v>6687843</v>
+        <v>6687935</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300601</v>
+        <v>130300845</v>
       </c>
       <c r="B40" t="n">
         <v>98920</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490648</v>
+        <v>490638</v>
       </c>
       <c r="R40" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,45 +4974,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300089</v>
+        <v>130300674</v>
       </c>
       <c r="B41" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490754</v>
+        <v>490640</v>
       </c>
       <c r="R41" t="n">
-        <v>6687921</v>
+        <v>6687937</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,7 +5081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300674</v>
+        <v>130299645</v>
       </c>
       <c r="B42" t="n">
         <v>98920</v>
@@ -5112,14 +5112,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490640</v>
+        <v>490670</v>
       </c>
       <c r="R42" t="n">
-        <v>6687937</v>
+        <v>6687843</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,7 +5188,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130300845</v>
+        <v>130299047</v>
       </c>
       <c r="B43" t="n">
         <v>98920</v>
@@ -5219,11 +5219,11 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490638</v>
+        <v>490706</v>
       </c>
       <c r="R43" t="n">
         <v>6687897</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,45 +5295,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299949</v>
+        <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490740</v>
+        <v>490689</v>
       </c>
       <c r="R44" t="n">
-        <v>6687892</v>
+        <v>6687918</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5365,7 +5370,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5375,7 +5380,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,7 +5412,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130298757</v>
+        <v>130299949</v>
       </c>
       <c r="B45" t="n">
         <v>98920</v>
@@ -5437,10 +5447,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490809</v>
+        <v>490740</v>
       </c>
       <c r="R45" t="n">
-        <v>6687859</v>
+        <v>6687892</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5472,7 +5482,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5482,7 +5492,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,38 +5519,47 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130299124</v>
+        <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5549,10 +5568,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490689</v>
+        <v>490823</v>
       </c>
       <c r="R46" t="n">
-        <v>6687918</v>
+        <v>6687809</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5584,7 +5603,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5594,12 +5613,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>I närheten.</t>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5626,7 +5645,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130298688</v>
+        <v>130298757</v>
       </c>
       <c r="B47" t="n">
         <v>98920</v>
@@ -5654,31 +5673,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490823</v>
+        <v>490809</v>
       </c>
       <c r="R47" t="n">
-        <v>6687809</v>
+        <v>6687859</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,7 +5715,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5720,12 +5725,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,47 +5752,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130298812</v>
+        <v>130299179</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5801,7 +5792,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490761</v>
+        <v>490663</v>
       </c>
       <c r="R48" t="n">
         <v>6687895</v>
@@ -5836,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5846,12 +5837,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 100.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5878,50 +5869,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R49" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5953,7 +5939,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5963,7 +5949,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5990,45 +5976,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299662</v>
+        <v>130299101</v>
       </c>
       <c r="B50" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490664</v>
+        <v>490685</v>
       </c>
       <c r="R50" t="n">
-        <v>6687847</v>
+        <v>6687923</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6060,7 +6051,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6070,7 +6061,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6097,38 +6088,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299179</v>
+        <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490663</v>
+        <v>490761</v>
       </c>
       <c r="R51" t="n">
         <v>6687895</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
         <v>98920</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130298464</v>
+        <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490854</v>
+        <v>490741</v>
       </c>
       <c r="R53" t="n">
-        <v>6687851</v>
+        <v>6687894</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130299966</v>
+        <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490741</v>
+        <v>490854</v>
       </c>
       <c r="R55" t="n">
-        <v>6687894</v>
+        <v>6687851</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,47 +6642,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130298364</v>
+        <v>130299999</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6682,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490775</v>
+        <v>490742</v>
       </c>
       <c r="R56" t="n">
-        <v>6687939</v>
+        <v>6687893</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6726,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6736,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6870,45 +6861,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>93010</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,50 +6977,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130299909</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>97166</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490723</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687910</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7052,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7062,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,45 +7084,59 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7159,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7169,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,54 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130300998</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490659</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687865</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300930</v>
+        <v>130300998</v>
       </c>
       <c r="B3" t="n">
         <v>98920</v>
@@ -813,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490628</v>
+        <v>490659</v>
       </c>
       <c r="R3" t="n">
-        <v>6687894</v>
+        <v>6687865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300146</v>
+        <v>130300930</v>
       </c>
       <c r="B4" t="n">
         <v>98920</v>
@@ -920,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490771</v>
+        <v>490628</v>
       </c>
       <c r="R4" t="n">
-        <v>6687913</v>
+        <v>6687894</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130299512</v>
+        <v>130300146</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490708</v>
+        <v>490771</v>
       </c>
       <c r="R5" t="n">
-        <v>6687780</v>
+        <v>6687913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298423</v>
+        <v>130299757</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490654</v>
       </c>
       <c r="R12" t="n">
-        <v>6687879</v>
+        <v>6687872</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130299757</v>
+        <v>130298405</v>
       </c>
       <c r="B13" t="n">
         <v>98920</v>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490654</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6687872</v>
+        <v>6687878</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -2002,17 +2002,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R14" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,59 +2095,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R15" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,50 +2207,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130298423</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687879</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3651,45 +3651,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130298471</v>
+        <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490854</v>
+        <v>490657</v>
       </c>
       <c r="R29" t="n">
-        <v>6687846</v>
+        <v>6687863</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3731,7 +3736,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3758,45 +3763,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299120</v>
+        <v>130299432</v>
       </c>
       <c r="B30" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490690</v>
+        <v>490697</v>
       </c>
       <c r="R30" t="n">
-        <v>6687921</v>
+        <v>6687828</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3828,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,7 +3848,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,45 +3875,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130299915</v>
+        <v>130300532</v>
       </c>
       <c r="B31" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490724</v>
+        <v>490688</v>
       </c>
       <c r="R31" t="n">
-        <v>6687908</v>
+        <v>6687940</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3935,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3945,7 +3960,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3972,7 +3992,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299013</v>
+        <v>130298471</v>
       </c>
       <c r="B32" t="n">
         <v>98920</v>
@@ -4000,31 +4020,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490722</v>
+        <v>490854</v>
       </c>
       <c r="R32" t="n">
-        <v>6687888</v>
+        <v>6687846</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4056,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4066,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4098,50 +4099,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130300987</v>
+        <v>130299120</v>
       </c>
       <c r="B33" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490657</v>
+        <v>490690</v>
       </c>
       <c r="R33" t="n">
-        <v>6687863</v>
+        <v>6687921</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4173,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4183,7 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,50 +4206,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300532</v>
+        <v>130299915</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490688</v>
+        <v>490724</v>
       </c>
       <c r="R34" t="n">
-        <v>6687940</v>
+        <v>6687908</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,12 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4327,38 +4313,47 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299432</v>
+        <v>130299013</v>
       </c>
       <c r="B35" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4367,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490697</v>
+        <v>490722</v>
       </c>
       <c r="R35" t="n">
-        <v>6687828</v>
+        <v>6687888</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4402,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4412,7 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,45 +4546,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300089</v>
+        <v>130300845</v>
       </c>
       <c r="B37" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490754</v>
+        <v>490638</v>
       </c>
       <c r="R37" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300601</v>
+        <v>130300674</v>
       </c>
       <c r="B38" t="n">
         <v>98920</v>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490648</v>
+        <v>490640</v>
       </c>
       <c r="R38" t="n">
-        <v>6687935</v>
+        <v>6687937</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,45 +4760,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130298958</v>
+        <v>130300601</v>
       </c>
       <c r="B39" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490730</v>
+        <v>490648</v>
       </c>
       <c r="R39" t="n">
-        <v>6687864</v>
+        <v>6687935</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300845</v>
+        <v>130299645</v>
       </c>
       <c r="B40" t="n">
         <v>98920</v>
@@ -4898,14 +4898,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490638</v>
+        <v>490670</v>
       </c>
       <c r="R40" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300674</v>
+        <v>130299047</v>
       </c>
       <c r="B41" t="n">
         <v>98920</v>
@@ -5005,14 +5005,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490640</v>
+        <v>490706</v>
       </c>
       <c r="R41" t="n">
-        <v>6687937</v>
+        <v>6687897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299645</v>
+        <v>130300089</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490670</v>
+        <v>490754</v>
       </c>
       <c r="R42" t="n">
-        <v>6687843</v>
+        <v>6687921</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R43" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5752,38 +5752,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299179</v>
+        <v>130298812</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5792,7 +5801,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490663</v>
+        <v>490761</v>
       </c>
       <c r="R48" t="n">
         <v>6687895</v>
@@ -5827,7 +5836,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,12 +5846,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5869,7 +5878,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B49" t="n">
         <v>98920</v>
@@ -5904,10 +5913,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R49" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5948,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,7 +5958,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6088,7 +6097,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130298812</v>
+        <v>130300215</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6116,31 +6125,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490761</v>
+        <v>490750</v>
       </c>
       <c r="R51" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6172,7 +6167,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6182,12 +6177,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,45 +6204,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299662</v>
+        <v>130299179</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490664</v>
+        <v>490663</v>
       </c>
       <c r="R52" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6279,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6289,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6754,45 +6754,59 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130300918</v>
+        <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490628</v>
+        <v>490775</v>
       </c>
       <c r="R57" t="n">
-        <v>6687894</v>
+        <v>6687939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6824,7 +6838,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6834,7 +6848,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6861,54 +6875,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B58" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R58" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6945,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6955,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,7 +6982,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299909</v>
+        <v>130300918</v>
       </c>
       <c r="B59" t="n">
         <v>97166</v>
@@ -7008,14 +7013,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490723</v>
+        <v>490628</v>
       </c>
       <c r="R59" t="n">
-        <v>6687910</v>
+        <v>6687894</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7052,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7062,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,59 +7089,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130299909</v>
       </c>
       <c r="B60" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490723</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687910</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7159,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7169,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7196,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>93010</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130300998</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490659</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300998</v>
+        <v>130300930</v>
       </c>
       <c r="B3" t="n">
         <v>98920</v>
@@ -823,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490659</v>
+        <v>490628</v>
       </c>
       <c r="R3" t="n">
-        <v>6687865</v>
+        <v>6687894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300930</v>
+        <v>130300146</v>
       </c>
       <c r="B4" t="n">
         <v>98920</v>
@@ -930,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490628</v>
+        <v>490771</v>
       </c>
       <c r="R4" t="n">
-        <v>6687894</v>
+        <v>6687913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300146</v>
+        <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490771</v>
+        <v>490708</v>
       </c>
       <c r="R5" t="n">
-        <v>6687913</v>
+        <v>6687780</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130299757</v>
+        <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490654</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6687872</v>
+        <v>6687879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298405</v>
+        <v>130300768</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490629</v>
       </c>
       <c r="R13" t="n">
-        <v>6687878</v>
+        <v>6687910</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298782</v>
+        <v>130299757</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -2002,31 +2002,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490803</v>
+        <v>490654</v>
       </c>
       <c r="R14" t="n">
-        <v>6687883</v>
+        <v>6687872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,50 +2086,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130300768</v>
+        <v>130298405</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490629</v>
+        <v>490825</v>
       </c>
       <c r="R15" t="n">
-        <v>6687910</v>
+        <v>6687878</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298423</v>
+        <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2204,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490832</v>
+        <v>490803</v>
       </c>
       <c r="R16" t="n">
-        <v>6687879</v>
+        <v>6687883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2635,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298529</v>
+        <v>130298375</v>
       </c>
       <c r="B20" t="n">
         <v>98920</v>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490885</v>
+        <v>490816</v>
       </c>
       <c r="R20" t="n">
-        <v>6687821</v>
+        <v>6687911</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,47 +2756,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298375</v>
+        <v>130299657</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490669</v>
       </c>
       <c r="R21" t="n">
-        <v>6687911</v>
+        <v>6687844</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,7 +2831,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2841,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,38 +2873,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130299657</v>
+        <v>130298529</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490669</v>
+        <v>490885</v>
       </c>
       <c r="R22" t="n">
-        <v>6687844</v>
+        <v>6687821</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2967,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3651,38 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300987</v>
+        <v>130300532</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490657</v>
+        <v>490688</v>
       </c>
       <c r="R29" t="n">
-        <v>6687863</v>
+        <v>6687940</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,50 +3768,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299432</v>
+        <v>130298471</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490697</v>
+        <v>490854</v>
       </c>
       <c r="R30" t="n">
-        <v>6687828</v>
+        <v>6687846</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,50 +3875,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130300532</v>
+        <v>130299120</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490688</v>
+        <v>490690</v>
       </c>
       <c r="R31" t="n">
-        <v>6687940</v>
+        <v>6687921</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3950,7 +3945,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,12 +3955,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,7 +3982,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130298471</v>
+        <v>130299915</v>
       </c>
       <c r="B32" t="n">
         <v>98920</v>
@@ -4027,10 +4017,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490854</v>
+        <v>490724</v>
       </c>
       <c r="R32" t="n">
-        <v>6687846</v>
+        <v>6687908</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4062,7 +4052,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4062,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4099,7 +4089,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299120</v>
+        <v>130299013</v>
       </c>
       <c r="B33" t="n">
         <v>98920</v>
@@ -4127,17 +4117,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490690</v>
+        <v>490722</v>
       </c>
       <c r="R33" t="n">
-        <v>6687921</v>
+        <v>6687888</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4169,7 +4173,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4183,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4206,45 +4215,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299915</v>
+        <v>130300987</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490724</v>
+        <v>490657</v>
       </c>
       <c r="R34" t="n">
-        <v>6687908</v>
+        <v>6687863</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4276,7 +4290,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4286,7 +4300,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,47 +4327,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299013</v>
+        <v>130299432</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4367,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490722</v>
+        <v>490697</v>
       </c>
       <c r="R35" t="n">
-        <v>6687888</v>
+        <v>6687828</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4402,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4412,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,45 +4546,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300845</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490638</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,45 +4653,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300674</v>
+        <v>130300089</v>
       </c>
       <c r="B38" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490640</v>
+        <v>490754</v>
       </c>
       <c r="R38" t="n">
-        <v>6687937</v>
+        <v>6687921</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300601</v>
+        <v>130300845</v>
       </c>
       <c r="B39" t="n">
         <v>98920</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490648</v>
+        <v>490638</v>
       </c>
       <c r="R39" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130299645</v>
+        <v>130300674</v>
       </c>
       <c r="B40" t="n">
         <v>98920</v>
@@ -4898,14 +4898,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490670</v>
+        <v>490640</v>
       </c>
       <c r="R40" t="n">
-        <v>6687843</v>
+        <v>6687937</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130299047</v>
+        <v>130300601</v>
       </c>
       <c r="B41" t="n">
         <v>98920</v>
@@ -5005,14 +5005,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490706</v>
+        <v>490648</v>
       </c>
       <c r="R41" t="n">
-        <v>6687897</v>
+        <v>6687935</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300089</v>
+        <v>130299645</v>
       </c>
       <c r="B42" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490754</v>
+        <v>490670</v>
       </c>
       <c r="R42" t="n">
-        <v>6687921</v>
+        <v>6687843</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B43" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R43" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5752,47 +5752,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130298812</v>
+        <v>130299101</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5801,10 +5792,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490761</v>
+        <v>490685</v>
       </c>
       <c r="R48" t="n">
-        <v>6687895</v>
+        <v>6687923</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5836,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5846,12 +5837,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5878,7 +5864,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299662</v>
+        <v>130300215</v>
       </c>
       <c r="B49" t="n">
         <v>98920</v>
@@ -5913,10 +5899,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490664</v>
+        <v>490750</v>
       </c>
       <c r="R49" t="n">
-        <v>6687847</v>
+        <v>6687940</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5948,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5958,7 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5985,10 +5971,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299101</v>
+        <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5996,16 +5982,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6025,10 +6011,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490685</v>
+        <v>490663</v>
       </c>
       <c r="R50" t="n">
-        <v>6687923</v>
+        <v>6687895</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6060,7 +6046,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6070,7 +6056,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6097,7 +6088,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130300215</v>
+        <v>130298812</v>
       </c>
       <c r="B51" t="n">
         <v>98920</v>
@@ -6125,17 +6116,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490750</v>
+        <v>490761</v>
       </c>
       <c r="R51" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6167,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6177,7 +6182,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6204,50 +6214,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299179</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490663</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6279,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6289,12 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6754,59 +6754,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130298364</v>
+        <v>130300918</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490775</v>
+        <v>490628</v>
       </c>
       <c r="R57" t="n">
-        <v>6687939</v>
+        <v>6687894</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6838,7 +6824,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6848,7 +6834,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6875,32 +6861,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130299909</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6910,10 +6896,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490723</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687910</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,7 +6931,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6955,7 +6941,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6982,45 +6968,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130300918</v>
+        <v>130299604</v>
       </c>
       <c r="B59" t="n">
-        <v>97166</v>
+        <v>93010</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490628</v>
+        <v>490666</v>
       </c>
       <c r="R59" t="n">
-        <v>6687894</v>
+        <v>6687830</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7052,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7062,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,45 +7084,59 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7159,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7169,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,54 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130298671</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490825</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687809</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130300998</v>
       </c>
       <c r="B3" t="n">
         <v>98920</v>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490659</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130300930</v>
       </c>
       <c r="B4" t="n">
         <v>98920</v>
@@ -930,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490628</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687894</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130300146</v>
       </c>
       <c r="B5" t="n">
         <v>98920</v>
@@ -1037,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490771</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,45 +1103,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130299512</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490708</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687780</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -4215,50 +4215,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300532</v>
+        <v>130299915</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490688</v>
+        <v>490724</v>
       </c>
       <c r="R34" t="n">
-        <v>6687940</v>
+        <v>6687908</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4290,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4300,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,45 +4322,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299915</v>
+        <v>130300532</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490724</v>
+        <v>490688</v>
       </c>
       <c r="R35" t="n">
-        <v>6687908</v>
+        <v>6687940</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4402,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4412,7 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6642,45 +6642,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299909</v>
+        <v>130299999</v>
       </c>
       <c r="B56" t="n">
-        <v>97166</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490723</v>
+        <v>490742</v>
       </c>
       <c r="R56" t="n">
-        <v>6687910</v>
+        <v>6687893</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,42 +6754,47 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299604</v>
+        <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6793,10 +6803,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490666</v>
+        <v>490775</v>
       </c>
       <c r="R57" t="n">
-        <v>6687830</v>
+        <v>6687939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6828,7 +6838,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6838,7 +6848,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6865,45 +6875,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130299214</v>
       </c>
       <c r="B58" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490665</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687861</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6945,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6955,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,50 +6982,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130300918</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>97166</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490628</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687894</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7052,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7062,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,59 +7089,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130299909</v>
       </c>
       <c r="B60" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490723</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687910</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7159,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7169,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7196,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>93010</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130298671</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490825</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687809</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300998</v>
+        <v>130298671</v>
       </c>
       <c r="B3" t="n">
         <v>98920</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490659</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6687865</v>
+        <v>6687809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300930</v>
+        <v>130300998</v>
       </c>
       <c r="B4" t="n">
         <v>98920</v>
@@ -920,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490628</v>
+        <v>490659</v>
       </c>
       <c r="R4" t="n">
-        <v>6687894</v>
+        <v>6687865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300146</v>
+        <v>130300930</v>
       </c>
       <c r="B5" t="n">
         <v>98920</v>
@@ -1027,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490771</v>
+        <v>490628</v>
       </c>
       <c r="R5" t="n">
-        <v>6687913</v>
+        <v>6687894</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130299512</v>
+        <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490708</v>
+        <v>490771</v>
       </c>
       <c r="R6" t="n">
-        <v>6687780</v>
+        <v>6687913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
         <v>98920</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
         <v>98920</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
         <v>98920</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3023,16 +3023,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3079,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300626</v>
+        <v>130300938</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,16 +3122,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3135,21 +3140,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490629</v>
       </c>
       <c r="R24" t="n">
-        <v>6687936</v>
+        <v>6687895</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4546,45 +4546,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300845</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490638</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300601</v>
+        <v>130299645</v>
       </c>
       <c r="B38" t="n">
         <v>98920</v>
@@ -4684,14 +4684,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490648</v>
+        <v>490670</v>
       </c>
       <c r="R38" t="n">
-        <v>6687935</v>
+        <v>6687843</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B39" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R39" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130299645</v>
+        <v>130300845</v>
       </c>
       <c r="B41" t="n">
         <v>98920</v>
@@ -5005,14 +5005,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490670</v>
+        <v>490638</v>
       </c>
       <c r="R41" t="n">
-        <v>6687843</v>
+        <v>6687897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,7 +5081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299047</v>
+        <v>130300674</v>
       </c>
       <c r="B42" t="n">
         <v>98920</v>
@@ -5112,14 +5112,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490706</v>
+        <v>490640</v>
       </c>
       <c r="R42" t="n">
-        <v>6687897</v>
+        <v>6687937</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,7 +5188,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130300674</v>
+        <v>130300601</v>
       </c>
       <c r="B43" t="n">
         <v>98920</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490640</v>
+        <v>490648</v>
       </c>
       <c r="R43" t="n">
-        <v>6687937</v>
+        <v>6687935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6642,50 +6642,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299999</v>
+        <v>130299909</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>97166</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490742</v>
+        <v>490723</v>
       </c>
       <c r="R56" t="n">
-        <v>6687893</v>
+        <v>6687910</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6727,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6754,47 +6749,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130298364</v>
+        <v>130299604</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>93010</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6803,10 +6793,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490775</v>
+        <v>490666</v>
       </c>
       <c r="R57" t="n">
-        <v>6687939</v>
+        <v>6687830</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6838,7 +6828,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6848,7 +6838,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6875,45 +6865,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130300918</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490628</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687894</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6955,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6982,45 +6972,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130300918</v>
+        <v>130299999</v>
       </c>
       <c r="B59" t="n">
-        <v>97166</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490628</v>
+        <v>490742</v>
       </c>
       <c r="R59" t="n">
-        <v>6687894</v>
+        <v>6687893</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7052,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7062,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,45 +7084,59 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7159,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7169,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,54 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B8" t="n">
         <v>98920</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130298856</v>
       </c>
       <c r="B9" t="n">
         <v>98920</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490770</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687828</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B10" t="n">
         <v>98920</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,50 +1755,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130300768</v>
+        <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490629</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6687910</v>
+        <v>6687879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298423</v>
+        <v>130300768</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490832</v>
+        <v>490629</v>
       </c>
       <c r="R13" t="n">
-        <v>6687879</v>
+        <v>6687910</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2994,50 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300626</v>
+        <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490855</v>
       </c>
       <c r="R23" t="n">
-        <v>6687936</v>
+        <v>6687847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3069,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,12 +3074,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,45 +3213,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130298467</v>
+        <v>130300626</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490855</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>6687847</v>
+        <v>6687936</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130300998</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490659</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490628</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130300146</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490771</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490708</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687780</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130298671</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490825</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298423</v>
+        <v>130298405</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490825</v>
       </c>
       <c r="R12" t="n">
-        <v>6687879</v>
+        <v>6687878</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130300768</v>
+        <v>130298423</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>92184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490629</v>
+        <v>490832</v>
       </c>
       <c r="R13" t="n">
-        <v>6687910</v>
+        <v>6687879</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1972,7 @@
         <v>130299757</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,17 +2109,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R15" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,59 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,32 +2314,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130298439</v>
+        <v>130299411</v>
       </c>
       <c r="B17" t="n">
-        <v>92026</v>
+        <v>98923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490826</v>
+        <v>490679</v>
       </c>
       <c r="R17" t="n">
-        <v>6687871</v>
+        <v>6687837</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130299411</v>
+        <v>130298439</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>92029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490679</v>
+        <v>490826</v>
       </c>
       <c r="R18" t="n">
-        <v>6687837</v>
+        <v>6687871</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,50 +2528,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299657</v>
+        <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490669</v>
+        <v>490666</v>
       </c>
       <c r="R19" t="n">
-        <v>6687844</v>
+        <v>6687855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299218</v>
+        <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,17 +2663,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490666</v>
+        <v>490885</v>
       </c>
       <c r="R20" t="n">
-        <v>6687855</v>
+        <v>6687821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298529</v>
+        <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,17 +2786,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2801,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490885</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6687821</v>
+        <v>6687911</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,47 +2877,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130298375</v>
+        <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490816</v>
+        <v>490669</v>
       </c>
       <c r="R22" t="n">
-        <v>6687911</v>
+        <v>6687844</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2967,7 +2962,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,7 +2997,7 @@
         <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,16 +3112,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3130,16 +3130,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3171,7 +3176,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3181,12 +3186,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300626</v>
+        <v>130300938</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,16 +3229,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3242,21 +3247,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490629</v>
       </c>
       <c r="R25" t="n">
-        <v>6687936</v>
+        <v>6687895</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130298421</v>
+        <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>97169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490831</v>
+        <v>490743</v>
       </c>
       <c r="R26" t="n">
-        <v>6687885</v>
+        <v>6687908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130299399</v>
+        <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>81165</v>
+        <v>91731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490680</v>
+        <v>490831</v>
       </c>
       <c r="R27" t="n">
-        <v>6687839</v>
+        <v>6687885</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300054</v>
+        <v>130299399</v>
       </c>
       <c r="B28" t="n">
-        <v>97166</v>
+        <v>81168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490743</v>
+        <v>490680</v>
       </c>
       <c r="R28" t="n">
-        <v>6687908</v>
+        <v>6687839</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,50 +3763,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300987</v>
+        <v>130298471</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490657</v>
+        <v>490854</v>
       </c>
       <c r="R30" t="n">
-        <v>6687863</v>
+        <v>6687846</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,7 +3843,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,10 +3870,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130299120</v>
       </c>
       <c r="B31" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,10 +3905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490690</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687921</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,10 +3977,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299120</v>
+        <v>130299915</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4017,10 +4012,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490690</v>
+        <v>490724</v>
       </c>
       <c r="R32" t="n">
-        <v>6687921</v>
+        <v>6687908</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4052,7 +4047,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4062,7 +4057,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,7 +4087,7 @@
         <v>130299013</v>
       </c>
       <c r="B33" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4215,45 +4210,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299915</v>
+        <v>130300987</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490724</v>
+        <v>490657</v>
       </c>
       <c r="R34" t="n">
-        <v>6687908</v>
+        <v>6687863</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130299645</v>
       </c>
       <c r="B37" t="n">
-        <v>97166</v>
+        <v>98923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490670</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687843</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299645</v>
+        <v>130299047</v>
       </c>
       <c r="B38" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490670</v>
+        <v>490706</v>
       </c>
       <c r="R38" t="n">
-        <v>6687843</v>
+        <v>6687897</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,7 +4870,7 @@
         <v>130300089</v>
       </c>
       <c r="B40" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>130300845</v>
       </c>
       <c r="B41" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>130300674</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>130300601</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,50 +5752,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R48" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,7 +5832,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5864,10 +5859,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299179</v>
+        <v>130299101</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5875,16 +5870,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5904,10 +5899,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490663</v>
+        <v>490685</v>
       </c>
       <c r="R49" t="n">
-        <v>6687895</v>
+        <v>6687923</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,12 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,47 +5971,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130298812</v>
+        <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6030,7 +6011,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490761</v>
+        <v>490663</v>
       </c>
       <c r="R50" t="n">
         <v>6687895</v>
@@ -6065,7 +6046,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6075,12 +6056,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 100.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299662</v>
+        <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,17 +6116,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490664</v>
+        <v>490761</v>
       </c>
       <c r="R51" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6177,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6187,7 +6182,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6324,7 +6324,7 @@
         <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>130299909</v>
       </c>
       <c r="B56" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>130299604</v>
       </c>
       <c r="B57" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6865,45 +6865,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130299999</v>
       </c>
       <c r="B58" t="n">
-        <v>97166</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490742</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687893</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6940,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6950,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,38 +6977,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130298364</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>98923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7012,10 +7026,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490775</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687939</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7061,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7071,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,10 +7098,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130299214</v>
       </c>
       <c r="B60" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7112,31 +7126,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490665</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687861</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130300918</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490628</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687894</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130300998</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130300146</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130298671</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>130298856</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130298552</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130300120</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,45 +1755,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298405</v>
+        <v>130300768</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490825</v>
+        <v>490629</v>
       </c>
       <c r="R12" t="n">
-        <v>6687878</v>
+        <v>6687910</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,7 +1870,7 @@
         <v>130298423</v>
       </c>
       <c r="B13" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
         <v>130299757</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298782</v>
+        <v>130298405</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,31 +2114,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490803</v>
+        <v>490825</v>
       </c>
       <c r="R15" t="n">
-        <v>6687883</v>
+        <v>6687878</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,50 +2193,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490803</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,32 +2314,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130299411</v>
+        <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>98923</v>
+        <v>92055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490679</v>
+        <v>490826</v>
       </c>
       <c r="R17" t="n">
-        <v>6687837</v>
+        <v>6687871</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298439</v>
+        <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>92029</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490826</v>
+        <v>490679</v>
       </c>
       <c r="R18" t="n">
-        <v>6687871</v>
+        <v>6687837</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,7 +2531,7 @@
         <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>130300938</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300054</v>
+        <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>97169</v>
+        <v>91757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490743</v>
+        <v>490831</v>
       </c>
       <c r="R26" t="n">
-        <v>6687908</v>
+        <v>6687885</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>91731</v>
+        <v>81194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R27" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130299399</v>
+        <v>130300054</v>
       </c>
       <c r="B28" t="n">
-        <v>81168</v>
+        <v>97195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490680</v>
+        <v>490743</v>
       </c>
       <c r="R28" t="n">
-        <v>6687839</v>
+        <v>6687908</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130299432</v>
+        <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490697</v>
+        <v>490657</v>
       </c>
       <c r="R29" t="n">
-        <v>6687828</v>
+        <v>6687863</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,45 +3763,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130298471</v>
+        <v>130300532</v>
       </c>
       <c r="B30" t="n">
-        <v>98923</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490854</v>
+        <v>490688</v>
       </c>
       <c r="R30" t="n">
-        <v>6687846</v>
+        <v>6687940</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3833,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3843,7 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3870,10 +3880,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130299120</v>
+        <v>130298471</v>
       </c>
       <c r="B31" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,10 +3915,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490690</v>
+        <v>490854</v>
       </c>
       <c r="R31" t="n">
-        <v>6687921</v>
+        <v>6687846</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3940,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3950,7 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3977,10 +3987,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299915</v>
+        <v>130299120</v>
       </c>
       <c r="B32" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490724</v>
+        <v>490690</v>
       </c>
       <c r="R32" t="n">
-        <v>6687908</v>
+        <v>6687921</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4047,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4057,7 +4067,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299013</v>
+        <v>130299915</v>
       </c>
       <c r="B33" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,31 +4122,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490722</v>
+        <v>490724</v>
       </c>
       <c r="R33" t="n">
-        <v>6687888</v>
+        <v>6687908</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4168,7 +4164,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4178,12 +4174,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,38 +4201,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300987</v>
+        <v>130299013</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490657</v>
+        <v>490722</v>
       </c>
       <c r="R34" t="n">
-        <v>6687863</v>
+        <v>6687888</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4295,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,38 +4327,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300532</v>
+        <v>130299432</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>57849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4367,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490688</v>
+        <v>490697</v>
       </c>
       <c r="R35" t="n">
-        <v>6687940</v>
+        <v>6687828</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4402,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4412,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130299645</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>98923</v>
+        <v>97195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490670</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687843</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299047</v>
+        <v>130299645</v>
       </c>
       <c r="B38" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490706</v>
+        <v>490670</v>
       </c>
       <c r="R38" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B39" t="n">
-        <v>97169</v>
+        <v>98949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R39" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,7 +4870,7 @@
         <v>130300089</v>
       </c>
       <c r="B40" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>130300845</v>
       </c>
       <c r="B41" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>130300674</v>
       </c>
       <c r="B42" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>130300601</v>
       </c>
       <c r="B43" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,45 +5752,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130300215</v>
+        <v>130299101</v>
       </c>
       <c r="B48" t="n">
-        <v>98923</v>
+        <v>57849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490750</v>
+        <v>490685</v>
       </c>
       <c r="R48" t="n">
-        <v>6687940</v>
+        <v>6687923</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5832,7 +5837,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,50 +5864,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>98949</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R49" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,7 +5974,7 @@
         <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299909</v>
+        <v>130300918</v>
       </c>
       <c r="B56" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6673,14 +6673,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490723</v>
+        <v>490628</v>
       </c>
       <c r="R56" t="n">
-        <v>6687910</v>
+        <v>6687894</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,54 +6749,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299604</v>
+        <v>130299909</v>
       </c>
       <c r="B57" t="n">
-        <v>93013</v>
+        <v>97195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490666</v>
+        <v>490723</v>
       </c>
       <c r="R57" t="n">
-        <v>6687830</v>
+        <v>6687910</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6828,7 +6819,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6838,7 +6829,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6865,10 +6856,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299999</v>
+        <v>130299604</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>93039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,27 +6867,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6905,10 +6900,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490742</v>
+        <v>490666</v>
       </c>
       <c r="R58" t="n">
-        <v>6687893</v>
+        <v>6687830</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,47 +6972,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130298364</v>
+        <v>130299999</v>
       </c>
       <c r="B59" t="n">
-        <v>98923</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7026,10 +7012,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490775</v>
+        <v>490742</v>
       </c>
       <c r="R59" t="n">
-        <v>6687939</v>
+        <v>6687893</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7061,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7071,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7098,10 +7084,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299214</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7126,17 +7112,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490665</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687861</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130300918</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>97169</v>
+        <v>98949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490628</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687894</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B8" t="n">
         <v>98949</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130298856</v>
       </c>
       <c r="B9" t="n">
         <v>98949</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490770</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687828</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B10" t="n">
         <v>98949</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -5752,50 +5752,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B48" t="n">
-        <v>57849</v>
+        <v>98949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R48" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,7 +5832,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5864,45 +5859,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130300215</v>
+        <v>130299179</v>
       </c>
       <c r="B49" t="n">
-        <v>98949</v>
+        <v>57852</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490750</v>
+        <v>490663</v>
       </c>
       <c r="R49" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5944,7 +5944,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5971,38 +5976,47 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299179</v>
+        <v>130298812</v>
       </c>
       <c r="B50" t="n">
-        <v>57852</v>
+        <v>98949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6011,7 +6025,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490663</v>
+        <v>490761</v>
       </c>
       <c r="R50" t="n">
         <v>6687895</v>
@@ -6046,7 +6060,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6056,12 +6070,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6088,7 +6102,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130298812</v>
+        <v>130299662</v>
       </c>
       <c r="B51" t="n">
         <v>98949</v>
@@ -6116,31 +6130,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490761</v>
+        <v>490664</v>
       </c>
       <c r="R51" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6182,12 +6182,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,45 +6209,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299662</v>
+        <v>130299101</v>
       </c>
       <c r="B52" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490664</v>
+        <v>490685</v>
       </c>
       <c r="R52" t="n">
-        <v>6687847</v>
+        <v>6687923</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130300998</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490659</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687865</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +795,7 @@
         <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300146</v>
+        <v>130298671</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490771</v>
+        <v>490825</v>
       </c>
       <c r="R4" t="n">
-        <v>6687913</v>
+        <v>6687809</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130299512</v>
+        <v>130300998</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490708</v>
+        <v>490659</v>
       </c>
       <c r="R5" t="n">
-        <v>6687780</v>
+        <v>6687865</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298671</v>
+        <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490825</v>
+        <v>490771</v>
       </c>
       <c r="R6" t="n">
-        <v>6687809</v>
+        <v>6687913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>130300120</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130298856</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130298552</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,50 +1755,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130300768</v>
+        <v>130299757</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490629</v>
+        <v>490654</v>
       </c>
       <c r="R12" t="n">
-        <v>6687910</v>
+        <v>6687872</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298423</v>
+        <v>130298405</v>
       </c>
       <c r="B13" t="n">
-        <v>92210</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490832</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6687879</v>
+        <v>6687878</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130299757</v>
+        <v>130298782</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,17 +2002,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490654</v>
+        <v>490803</v>
       </c>
       <c r="R14" t="n">
-        <v>6687872</v>
+        <v>6687883</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298405</v>
+        <v>130298423</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>92211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490825</v>
+        <v>490832</v>
       </c>
       <c r="R15" t="n">
-        <v>6687878</v>
+        <v>6687879</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,59 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2317,7 @@
         <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R23" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,7 +3074,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,45 +3223,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300938</v>
+        <v>130298467</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490629</v>
+        <v>490855</v>
       </c>
       <c r="R25" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3303,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130298421</v>
+        <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>91757</v>
+        <v>97196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490831</v>
+        <v>490743</v>
       </c>
       <c r="R26" t="n">
-        <v>6687885</v>
+        <v>6687908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130299399</v>
+        <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>81194</v>
+        <v>91758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490680</v>
+        <v>490831</v>
       </c>
       <c r="R27" t="n">
-        <v>6687839</v>
+        <v>6687885</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300054</v>
+        <v>130299399</v>
       </c>
       <c r="B28" t="n">
-        <v>97195</v>
+        <v>81194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490743</v>
+        <v>490680</v>
       </c>
       <c r="R28" t="n">
-        <v>6687908</v>
+        <v>6687839</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,38 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300987</v>
+        <v>130300532</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490657</v>
+        <v>490688</v>
       </c>
       <c r="R29" t="n">
-        <v>6687863</v>
+        <v>6687940</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,50 +3768,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300532</v>
+        <v>130298471</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>98950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490688</v>
+        <v>490854</v>
       </c>
       <c r="R30" t="n">
-        <v>6687940</v>
+        <v>6687846</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3848,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130299120</v>
       </c>
       <c r="B31" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490690</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687921</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3950,7 +3945,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3955,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,10 +3982,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299120</v>
+        <v>130299915</v>
       </c>
       <c r="B32" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490690</v>
+        <v>490724</v>
       </c>
       <c r="R32" t="n">
-        <v>6687921</v>
+        <v>6687908</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4057,7 +4052,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,7 +4062,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,10 +4089,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299915</v>
+        <v>130299013</v>
       </c>
       <c r="B33" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,17 +4117,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490724</v>
+        <v>490722</v>
       </c>
       <c r="R33" t="n">
-        <v>6687908</v>
+        <v>6687888</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4164,7 +4173,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4174,7 +4183,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4201,47 +4215,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299013</v>
+        <v>130300987</v>
       </c>
       <c r="B34" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490722</v>
+        <v>490657</v>
       </c>
       <c r="R34" t="n">
-        <v>6687888</v>
+        <v>6687863</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4290,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,12 +4300,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130299645</v>
       </c>
       <c r="B37" t="n">
-        <v>97195</v>
+        <v>98950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490670</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687843</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299645</v>
+        <v>130299047</v>
       </c>
       <c r="B38" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490670</v>
+        <v>490706</v>
       </c>
       <c r="R38" t="n">
-        <v>6687843</v>
+        <v>6687897</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130299047</v>
+        <v>130300089</v>
       </c>
       <c r="B39" t="n">
-        <v>98949</v>
+        <v>97196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490706</v>
+        <v>490754</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687921</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,45 +4867,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300089</v>
+        <v>130300845</v>
       </c>
       <c r="B40" t="n">
-        <v>97195</v>
+        <v>98950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490754</v>
+        <v>490638</v>
       </c>
       <c r="R40" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300845</v>
+        <v>130300674</v>
       </c>
       <c r="B41" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490638</v>
+        <v>490640</v>
       </c>
       <c r="R41" t="n">
-        <v>6687897</v>
+        <v>6687937</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300674</v>
+        <v>130300601</v>
       </c>
       <c r="B42" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490640</v>
+        <v>490648</v>
       </c>
       <c r="R42" t="n">
-        <v>6687937</v>
+        <v>6687935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,45 +5188,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130300601</v>
+        <v>130298958</v>
       </c>
       <c r="B43" t="n">
-        <v>98949</v>
+        <v>97196</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490648</v>
+        <v>490730</v>
       </c>
       <c r="R43" t="n">
-        <v>6687935</v>
+        <v>6687864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,45 +5752,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130300215</v>
+        <v>130299101</v>
       </c>
       <c r="B48" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490750</v>
+        <v>490685</v>
       </c>
       <c r="R48" t="n">
-        <v>6687940</v>
+        <v>6687923</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5832,7 +5837,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5979,7 +5984,7 @@
         <v>130298812</v>
       </c>
       <c r="B50" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6105,7 +6110,7 @@
         <v>130299662</v>
       </c>
       <c r="B51" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6209,50 +6214,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B52" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R52" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130299966</v>
+        <v>130298795</v>
       </c>
       <c r="B53" t="n">
-        <v>97195</v>
+        <v>98950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490741</v>
+        <v>490776</v>
       </c>
       <c r="R53" t="n">
-        <v>6687894</v>
+        <v>6687899</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6428,10 +6428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130298795</v>
+        <v>130298464</v>
       </c>
       <c r="B54" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490776</v>
+        <v>490854</v>
       </c>
       <c r="R54" t="n">
-        <v>6687899</v>
+        <v>6687851</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130298464</v>
+        <v>130299966</v>
       </c>
       <c r="B55" t="n">
-        <v>98949</v>
+        <v>97196</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490854</v>
+        <v>490741</v>
       </c>
       <c r="R55" t="n">
-        <v>6687851</v>
+        <v>6687894</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,45 +6642,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130300918</v>
+        <v>130299999</v>
       </c>
       <c r="B56" t="n">
-        <v>97195</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490628</v>
+        <v>490742</v>
       </c>
       <c r="R56" t="n">
-        <v>6687894</v>
+        <v>6687893</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,45 +6754,59 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299909</v>
+        <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>97195</v>
+        <v>98950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490723</v>
+        <v>490775</v>
       </c>
       <c r="R57" t="n">
-        <v>6687910</v>
+        <v>6687939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6819,7 +6838,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6829,7 +6848,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6856,54 +6875,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B58" t="n">
-        <v>93039</v>
+        <v>98950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R58" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6945,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6955,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,50 +6982,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130300918</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>97196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490628</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687894</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7052,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7062,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,59 +7089,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130299909</v>
       </c>
       <c r="B60" t="n">
-        <v>98949</v>
+        <v>97196</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490723</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687910</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7159,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7169,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7196,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B61" t="n">
-        <v>98949</v>
+        <v>93040</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300930</v>
+        <v>130298671</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490628</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6687894</v>
+        <v>6687809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130298671</v>
+        <v>130300998</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490825</v>
+        <v>490659</v>
       </c>
       <c r="R4" t="n">
-        <v>6687809</v>
+        <v>6687865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300998</v>
+        <v>130300930</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490659</v>
+        <v>490628</v>
       </c>
       <c r="R5" t="n">
-        <v>6687865</v>
+        <v>6687894</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R8" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>130298856</v>
       </c>
       <c r="B9" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,45 +1755,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130299757</v>
+        <v>130300768</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490654</v>
+        <v>490629</v>
       </c>
       <c r="R12" t="n">
-        <v>6687872</v>
+        <v>6687910</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
         <v>130298405</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298782</v>
+        <v>130299757</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,31 +2002,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490803</v>
+        <v>490654</v>
       </c>
       <c r="R14" t="n">
-        <v>6687883</v>
+        <v>6687872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2089,7 @@
         <v>130298423</v>
       </c>
       <c r="B15" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,50 +2193,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490803</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2317,7 @@
         <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490855</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3074,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300626</v>
+        <v>130300938</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,16 +3112,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3135,21 +3130,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490629</v>
       </c>
       <c r="R24" t="n">
-        <v>6687936</v>
+        <v>6687895</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3181,7 +3171,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3181,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,45 +3213,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130298467</v>
+        <v>130300626</v>
       </c>
       <c r="B25" t="n">
-        <v>98950</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490855</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>6687847</v>
+        <v>6687936</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,7 +3333,7 @@
         <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3651,38 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300532</v>
+        <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490688</v>
+        <v>490657</v>
       </c>
       <c r="R29" t="n">
-        <v>6687940</v>
+        <v>6687863</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3736,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,45 +3763,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130298471</v>
+        <v>130299432</v>
       </c>
       <c r="B30" t="n">
-        <v>98950</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490854</v>
+        <v>490697</v>
       </c>
       <c r="R30" t="n">
-        <v>6687846</v>
+        <v>6687828</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130299120</v>
+        <v>130299013</v>
       </c>
       <c r="B31" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3903,17 +3903,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490690</v>
+        <v>490722</v>
       </c>
       <c r="R31" t="n">
-        <v>6687921</v>
+        <v>6687888</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3945,7 +3959,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3955,7 +3969,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,10 +4001,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299915</v>
+        <v>130298471</v>
       </c>
       <c r="B32" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4017,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490724</v>
+        <v>490854</v>
       </c>
       <c r="R32" t="n">
-        <v>6687908</v>
+        <v>6687846</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4052,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4062,7 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,10 +4108,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299013</v>
+        <v>130299120</v>
       </c>
       <c r="B33" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4117,31 +4136,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490722</v>
+        <v>490690</v>
       </c>
       <c r="R33" t="n">
-        <v>6687888</v>
+        <v>6687921</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4173,7 +4178,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4183,12 +4188,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4215,50 +4215,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300987</v>
+        <v>130299915</v>
       </c>
       <c r="B34" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490657</v>
+        <v>490724</v>
       </c>
       <c r="R34" t="n">
-        <v>6687863</v>
+        <v>6687908</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4290,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4300,7 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4327,38 +4322,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299432</v>
+        <v>130300532</v>
       </c>
       <c r="B35" t="n">
-        <v>57849</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4367,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490697</v>
+        <v>490688</v>
       </c>
       <c r="R35" t="n">
-        <v>6687828</v>
+        <v>6687940</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4402,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4412,7 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130299645</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>98950</v>
+        <v>97197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490670</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687843</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,32 +4653,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299047</v>
+        <v>130300089</v>
       </c>
       <c r="B38" t="n">
-        <v>98950</v>
+        <v>97197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490706</v>
+        <v>490754</v>
       </c>
       <c r="R38" t="n">
-        <v>6687897</v>
+        <v>6687921</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,45 +4760,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300089</v>
+        <v>130300845</v>
       </c>
       <c r="B39" t="n">
-        <v>97196</v>
+        <v>98951</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490754</v>
+        <v>490638</v>
       </c>
       <c r="R39" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300845</v>
+        <v>130300674</v>
       </c>
       <c r="B40" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490638</v>
+        <v>490640</v>
       </c>
       <c r="R40" t="n">
-        <v>6687897</v>
+        <v>6687937</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300674</v>
+        <v>130300601</v>
       </c>
       <c r="B41" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490640</v>
+        <v>490648</v>
       </c>
       <c r="R41" t="n">
-        <v>6687937</v>
+        <v>6687935</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300601</v>
+        <v>130299645</v>
       </c>
       <c r="B42" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5112,14 +5112,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490648</v>
+        <v>490670</v>
       </c>
       <c r="R42" t="n">
-        <v>6687935</v>
+        <v>6687843</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B43" t="n">
-        <v>97196</v>
+        <v>98951</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R43" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,50 +5752,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B48" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R48" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,7 +5832,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5864,38 +5859,47 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299179</v>
+        <v>130298812</v>
       </c>
       <c r="B49" t="n">
-        <v>57852</v>
+        <v>98951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5904,7 +5908,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490663</v>
+        <v>490761</v>
       </c>
       <c r="R49" t="n">
         <v>6687895</v>
@@ -5939,7 +5943,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,12 +5953,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,10 +5985,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130298812</v>
+        <v>130299662</v>
       </c>
       <c r="B50" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,31 +6013,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490761</v>
+        <v>490664</v>
       </c>
       <c r="R50" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6055,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6075,12 +6065,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,45 +6092,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299662</v>
+        <v>130299101</v>
       </c>
       <c r="B51" t="n">
-        <v>98950</v>
+        <v>57849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490664</v>
+        <v>490685</v>
       </c>
       <c r="R51" t="n">
-        <v>6687847</v>
+        <v>6687923</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6177,7 +6167,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6187,7 +6177,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,45 +6204,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299179</v>
       </c>
       <c r="B52" t="n">
-        <v>98950</v>
+        <v>57852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490663</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6279,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6289,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130298795</v>
+        <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>98950</v>
+        <v>97197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490776</v>
+        <v>490741</v>
       </c>
       <c r="R53" t="n">
-        <v>6687899</v>
+        <v>6687894</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6428,10 +6428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130298464</v>
+        <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490854</v>
+        <v>490776</v>
       </c>
       <c r="R54" t="n">
-        <v>6687851</v>
+        <v>6687899</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130299966</v>
+        <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>97196</v>
+        <v>98951</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490741</v>
+        <v>490854</v>
       </c>
       <c r="R55" t="n">
-        <v>6687894</v>
+        <v>6687851</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,50 +6642,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299999</v>
+        <v>130299909</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>97197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490742</v>
+        <v>490723</v>
       </c>
       <c r="R56" t="n">
-        <v>6687893</v>
+        <v>6687910</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6727,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6757,7 +6752,7 @@
         <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6875,45 +6870,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130300918</v>
       </c>
       <c r="B58" t="n">
-        <v>98950</v>
+        <v>97197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490628</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687894</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,7 +6940,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6955,7 +6950,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6982,45 +6977,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130300918</v>
+        <v>130299604</v>
       </c>
       <c r="B59" t="n">
-        <v>97196</v>
+        <v>93041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490628</v>
+        <v>490666</v>
       </c>
       <c r="R59" t="n">
-        <v>6687894</v>
+        <v>6687830</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7052,7 +7056,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7062,7 +7066,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,45 +7093,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130299999</v>
       </c>
       <c r="B60" t="n">
-        <v>97196</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490742</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687893</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7159,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7169,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,54 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299604</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>93040</v>
+        <v>98951</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490666</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687830</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130298671</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490825</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687809</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130299512</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490708</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687780</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>130300998</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130300930</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298552</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490897</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687798</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
         <v>130300120</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,50 +1755,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130300768</v>
+        <v>130299757</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490629</v>
+        <v>490654</v>
       </c>
       <c r="R12" t="n">
-        <v>6687910</v>
+        <v>6687872</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
         <v>130298405</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130299757</v>
+        <v>130298782</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,17 +2002,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490654</v>
+        <v>490803</v>
       </c>
       <c r="R14" t="n">
-        <v>6687872</v>
+        <v>6687883</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,45 +2095,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298423</v>
+        <v>130300768</v>
       </c>
       <c r="B15" t="n">
-        <v>92212</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490832</v>
+        <v>490629</v>
       </c>
       <c r="R15" t="n">
-        <v>6687879</v>
+        <v>6687910</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298782</v>
+        <v>130298423</v>
       </c>
       <c r="B16" t="n">
-        <v>98951</v>
+        <v>92214</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,48 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490803</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6687883</v>
+        <v>6687879</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2317,7 @@
         <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R23" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,7 +3074,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,16 +3117,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3130,16 +3135,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3171,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3181,12 +3191,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,50 +3223,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300626</v>
+        <v>130298467</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>98953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490855</v>
       </c>
       <c r="R25" t="n">
-        <v>6687936</v>
+        <v>6687847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3303,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,7 +3333,7 @@
         <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>130299399</v>
       </c>
       <c r="B28" t="n">
-        <v>81194</v>
+        <v>81196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,38 +3763,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299432</v>
+        <v>130300532</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490697</v>
+        <v>490688</v>
       </c>
       <c r="R30" t="n">
-        <v>6687828</v>
+        <v>6687940</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,7 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,47 +3880,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130299013</v>
+        <v>130299432</v>
       </c>
       <c r="B31" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3924,10 +3920,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490722</v>
+        <v>490697</v>
       </c>
       <c r="R31" t="n">
-        <v>6687888</v>
+        <v>6687828</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3959,7 +3955,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,12 +3965,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,7 +3995,7 @@
         <v>130298471</v>
       </c>
       <c r="B32" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4111,7 +4102,7 @@
         <v>130299120</v>
       </c>
       <c r="B33" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4209,7 @@
         <v>130299915</v>
       </c>
       <c r="B34" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4322,38 +4313,47 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300532</v>
+        <v>130299013</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>98953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490688</v>
+        <v>490722</v>
       </c>
       <c r="R35" t="n">
-        <v>6687940</v>
+        <v>6687888</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Urholkad märg.</t>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>130300089</v>
       </c>
       <c r="B38" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>130300845</v>
       </c>
       <c r="B39" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>130300674</v>
       </c>
       <c r="B40" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>130300601</v>
       </c>
       <c r="B41" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>130299645</v>
       </c>
       <c r="B42" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>130299047</v>
       </c>
       <c r="B43" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,45 +5752,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130300215</v>
+        <v>130299101</v>
       </c>
       <c r="B48" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490750</v>
+        <v>490685</v>
       </c>
       <c r="R48" t="n">
-        <v>6687940</v>
+        <v>6687923</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5832,7 +5837,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,47 +5864,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130298812</v>
+        <v>130299179</v>
       </c>
       <c r="B49" t="n">
-        <v>98951</v>
+        <v>57854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5908,7 +5904,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490761</v>
+        <v>490663</v>
       </c>
       <c r="R49" t="n">
         <v>6687895</v>
@@ -5943,7 +5939,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5953,12 +5949,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 100.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5985,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299662</v>
+        <v>130298812</v>
       </c>
       <c r="B50" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,17 +6009,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490664</v>
+        <v>490761</v>
       </c>
       <c r="R50" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6055,7 +6065,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6065,7 +6075,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6092,50 +6107,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299101</v>
+        <v>130299662</v>
       </c>
       <c r="B51" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490685</v>
+        <v>490664</v>
       </c>
       <c r="R51" t="n">
-        <v>6687923</v>
+        <v>6687847</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6167,7 +6177,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6177,7 +6187,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6204,50 +6214,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299179</v>
+        <v>130300215</v>
       </c>
       <c r="B52" t="n">
-        <v>57852</v>
+        <v>98953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490663</v>
+        <v>490750</v>
       </c>
       <c r="R52" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6279,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6289,12 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130299966</v>
+        <v>130298795</v>
       </c>
       <c r="B53" t="n">
-        <v>97197</v>
+        <v>98953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490741</v>
+        <v>490776</v>
       </c>
       <c r="R53" t="n">
-        <v>6687894</v>
+        <v>6687899</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6428,10 +6428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130298795</v>
+        <v>130298464</v>
       </c>
       <c r="B54" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490776</v>
+        <v>490854</v>
       </c>
       <c r="R54" t="n">
-        <v>6687899</v>
+        <v>6687851</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130298464</v>
+        <v>130299966</v>
       </c>
       <c r="B55" t="n">
-        <v>98951</v>
+        <v>97199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490854</v>
+        <v>490741</v>
       </c>
       <c r="R55" t="n">
-        <v>6687851</v>
+        <v>6687894</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,45 +6642,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299909</v>
+        <v>130299999</v>
       </c>
       <c r="B56" t="n">
-        <v>97197</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490723</v>
+        <v>490742</v>
       </c>
       <c r="R56" t="n">
-        <v>6687910</v>
+        <v>6687893</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6752,7 +6757,7 @@
         <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6870,45 +6875,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130299214</v>
       </c>
       <c r="B58" t="n">
-        <v>97197</v>
+        <v>98953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490665</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687861</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6945,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6955,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,54 +6982,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299604</v>
+        <v>130300918</v>
       </c>
       <c r="B59" t="n">
-        <v>93041</v>
+        <v>97199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490666</v>
+        <v>490628</v>
       </c>
       <c r="R59" t="n">
-        <v>6687830</v>
+        <v>6687894</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7056,7 +7052,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7066,7 +7062,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7093,50 +7089,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299999</v>
+        <v>130299909</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>97199</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490742</v>
+        <v>490723</v>
       </c>
       <c r="R60" t="n">
-        <v>6687893</v>
+        <v>6687910</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7159,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7169,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7196,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B61" t="n">
-        <v>98951</v>
+        <v>93043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130298671</v>
+        <v>130300998</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490825</v>
+        <v>490659</v>
       </c>
       <c r="R2" t="n">
-        <v>6687809</v>
+        <v>6687865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130299512</v>
+        <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490708</v>
+        <v>490628</v>
       </c>
       <c r="R3" t="n">
-        <v>6687780</v>
+        <v>6687894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130300146</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490771</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490708</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687780</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130298671</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490825</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B9" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130299757</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>130298405</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>130298782</v>
       </c>
       <c r="B14" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>130298423</v>
       </c>
       <c r="B16" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,45 +2528,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299218</v>
+        <v>130299657</v>
       </c>
       <c r="B19" t="n">
-        <v>98953</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490666</v>
+        <v>490669</v>
       </c>
       <c r="R19" t="n">
-        <v>6687855</v>
+        <v>6687844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2613,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298529</v>
+        <v>130299218</v>
       </c>
       <c r="B20" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,31 +2673,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490885</v>
+        <v>490666</v>
       </c>
       <c r="R20" t="n">
-        <v>6687821</v>
+        <v>6687855</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2725,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298375</v>
+        <v>130298529</v>
       </c>
       <c r="B21" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,17 +2782,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490885</v>
       </c>
       <c r="R21" t="n">
-        <v>6687911</v>
+        <v>6687821</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,38 +2873,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130299657</v>
+        <v>130298375</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490669</v>
+        <v>490816</v>
       </c>
       <c r="R22" t="n">
-        <v>6687844</v>
+        <v>6687911</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2967,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3023,16 +3023,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3079,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300626</v>
+        <v>130300938</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,16 +3122,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3135,21 +3140,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490629</v>
       </c>
       <c r="R24" t="n">
-        <v>6687936</v>
+        <v>6687895</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,7 +3226,7 @@
         <v>130298467</v>
       </c>
       <c r="B25" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300054</v>
+        <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>97199</v>
+        <v>91761</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490743</v>
+        <v>490831</v>
       </c>
       <c r="R26" t="n">
-        <v>6687908</v>
+        <v>6687885</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>91761</v>
+        <v>81196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R27" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130299399</v>
+        <v>130300054</v>
       </c>
       <c r="B28" t="n">
-        <v>81196</v>
+        <v>97203</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490680</v>
+        <v>490743</v>
       </c>
       <c r="R28" t="n">
-        <v>6687839</v>
+        <v>6687908</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,7 +3995,7 @@
         <v>130298471</v>
       </c>
       <c r="B32" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>130299120</v>
       </c>
       <c r="B33" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>130299915</v>
       </c>
       <c r="B34" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>130299013</v>
       </c>
       <c r="B35" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,45 +4546,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130300845</v>
       </c>
       <c r="B37" t="n">
-        <v>97199</v>
+        <v>98957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490638</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,45 +4653,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300089</v>
+        <v>130300674</v>
       </c>
       <c r="B38" t="n">
-        <v>97199</v>
+        <v>98957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490754</v>
+        <v>490640</v>
       </c>
       <c r="R38" t="n">
-        <v>6687921</v>
+        <v>6687937</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300845</v>
+        <v>130300601</v>
       </c>
       <c r="B39" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490638</v>
+        <v>490648</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687935</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,45 +4867,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300674</v>
+        <v>130298958</v>
       </c>
       <c r="B40" t="n">
-        <v>98953</v>
+        <v>97203</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490640</v>
+        <v>490730</v>
       </c>
       <c r="R40" t="n">
-        <v>6687937</v>
+        <v>6687864</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,45 +4974,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300601</v>
+        <v>130300089</v>
       </c>
       <c r="B41" t="n">
-        <v>98953</v>
+        <v>97203</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490648</v>
+        <v>490754</v>
       </c>
       <c r="R41" t="n">
-        <v>6687935</v>
+        <v>6687921</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,7 +5084,7 @@
         <v>130299645</v>
       </c>
       <c r="B42" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>130299047</v>
       </c>
       <c r="B43" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5295,50 +5295,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299124</v>
+        <v>130299949</v>
       </c>
       <c r="B44" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490689</v>
+        <v>490740</v>
       </c>
       <c r="R44" t="n">
-        <v>6687918</v>
+        <v>6687892</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5370,7 +5365,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5380,12 +5375,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,10 +5402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130299949</v>
+        <v>130298688</v>
       </c>
       <c r="B45" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5440,17 +5430,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490740</v>
+        <v>490823</v>
       </c>
       <c r="R45" t="n">
-        <v>6687892</v>
+        <v>6687809</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5482,7 +5486,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5492,7 +5496,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5519,10 +5528,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298688</v>
+        <v>130298757</v>
       </c>
       <c r="B46" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5547,31 +5556,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490823</v>
+        <v>490809</v>
       </c>
       <c r="R46" t="n">
-        <v>6687809</v>
+        <v>6687859</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5603,7 +5598,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5613,12 +5608,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,45 +5635,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130298757</v>
+        <v>130299124</v>
       </c>
       <c r="B47" t="n">
-        <v>98953</v>
+        <v>57851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490809</v>
+        <v>490689</v>
       </c>
       <c r="R47" t="n">
-        <v>6687859</v>
+        <v>6687918</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5715,7 +5710,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5725,7 +5720,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,50 +5864,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299179</v>
+        <v>130300215</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490663</v>
+        <v>490750</v>
       </c>
       <c r="R49" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,12 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,47 +5971,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130298812</v>
+        <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>98953</v>
+        <v>57854</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6030,7 +6011,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490761</v>
+        <v>490663</v>
       </c>
       <c r="R50" t="n">
         <v>6687895</v>
@@ -6065,7 +6046,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6075,12 +6056,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 100.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299662</v>
+        <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,17 +6116,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490664</v>
+        <v>490761</v>
       </c>
       <c r="R51" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6177,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6187,7 +6182,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130298795</v>
+        <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>98953</v>
+        <v>97203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490776</v>
+        <v>490741</v>
       </c>
       <c r="R53" t="n">
-        <v>6687899</v>
+        <v>6687894</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6428,10 +6428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130298464</v>
+        <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490854</v>
+        <v>490776</v>
       </c>
       <c r="R54" t="n">
-        <v>6687851</v>
+        <v>6687899</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130299966</v>
+        <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>97199</v>
+        <v>98957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490741</v>
+        <v>490854</v>
       </c>
       <c r="R55" t="n">
-        <v>6687894</v>
+        <v>6687851</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,50 +6642,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299999</v>
+        <v>130300918</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>97203</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490742</v>
+        <v>490628</v>
       </c>
       <c r="R56" t="n">
-        <v>6687893</v>
+        <v>6687894</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6727,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6754,59 +6749,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130298364</v>
+        <v>130299909</v>
       </c>
       <c r="B57" t="n">
-        <v>98953</v>
+        <v>97203</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490775</v>
+        <v>490723</v>
       </c>
       <c r="R57" t="n">
-        <v>6687939</v>
+        <v>6687910</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6838,7 +6819,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6848,7 +6829,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6875,45 +6856,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B58" t="n">
-        <v>98953</v>
+        <v>93047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6955,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6982,45 +6972,59 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130300918</v>
+        <v>130298364</v>
       </c>
       <c r="B59" t="n">
-        <v>97199</v>
+        <v>98957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490628</v>
+        <v>490775</v>
       </c>
       <c r="R59" t="n">
-        <v>6687894</v>
+        <v>6687939</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7052,7 +7056,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7062,7 +7066,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,32 +7093,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130299214</v>
       </c>
       <c r="B60" t="n">
-        <v>97199</v>
+        <v>98957</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7124,10 +7128,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490665</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687861</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7159,7 +7163,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7169,7 +7173,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,10 +7200,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299604</v>
+        <v>130299999</v>
       </c>
       <c r="B61" t="n">
-        <v>93043</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,31 +7211,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490666</v>
+        <v>490742</v>
       </c>
       <c r="R61" t="n">
-        <v>6687830</v>
+        <v>6687893</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130300998</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490659</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687865</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300930</v>
+        <v>130298671</v>
       </c>
       <c r="B3" t="n">
         <v>98957</v>
@@ -813,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490628</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6687894</v>
+        <v>6687809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300146</v>
+        <v>130300998</v>
       </c>
       <c r="B4" t="n">
         <v>98957</v>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490771</v>
+        <v>490659</v>
       </c>
       <c r="R4" t="n">
-        <v>6687913</v>
+        <v>6687865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130299512</v>
+        <v>130300930</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490708</v>
+        <v>490628</v>
       </c>
       <c r="R5" t="n">
-        <v>6687780</v>
+        <v>6687894</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298671</v>
+        <v>130300146</v>
       </c>
       <c r="B6" t="n">
         <v>98957</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490825</v>
+        <v>490771</v>
       </c>
       <c r="R6" t="n">
-        <v>6687809</v>
+        <v>6687913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B8" t="n">
         <v>98957</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R8" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
         <v>98957</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130299757</v>
+        <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>98957</v>
+        <v>92220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490654</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6687872</v>
+        <v>6687879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B13" t="n">
         <v>98957</v>
@@ -1895,17 +1890,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R13" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298782</v>
+        <v>130299757</v>
       </c>
       <c r="B14" t="n">
         <v>98957</v>
@@ -2002,31 +2011,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490803</v>
+        <v>490654</v>
       </c>
       <c r="R14" t="n">
-        <v>6687883</v>
+        <v>6687872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2063,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,50 +2095,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130300768</v>
+        <v>130298405</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490629</v>
+        <v>490825</v>
       </c>
       <c r="R15" t="n">
-        <v>6687910</v>
+        <v>6687878</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,45 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298423</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>92220</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490832</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687879</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,50 +2528,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299657</v>
+        <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490669</v>
+        <v>490666</v>
       </c>
       <c r="R19" t="n">
-        <v>6687844</v>
+        <v>6687855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299218</v>
+        <v>130298529</v>
       </c>
       <c r="B20" t="n">
         <v>98957</v>
@@ -2673,17 +2663,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490666</v>
+        <v>490885</v>
       </c>
       <c r="R20" t="n">
-        <v>6687855</v>
+        <v>6687821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,7 +2756,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298529</v>
+        <v>130298375</v>
       </c>
       <c r="B21" t="n">
         <v>98957</v>
@@ -2782,17 +2786,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2801,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490885</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6687821</v>
+        <v>6687911</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,47 +2877,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130298375</v>
+        <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490816</v>
+        <v>490669</v>
       </c>
       <c r="R22" t="n">
-        <v>6687911</v>
+        <v>6687844</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2967,7 +2962,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300626</v>
+        <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3023,21 +3023,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490629</v>
       </c>
       <c r="R23" t="n">
-        <v>6687936</v>
+        <v>6687895</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3069,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,12 +3074,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,16 +3117,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3140,16 +3135,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3651,38 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300987</v>
+        <v>130300532</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490657</v>
+        <v>490688</v>
       </c>
       <c r="R29" t="n">
-        <v>6687863</v>
+        <v>6687940</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,38 +3768,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300532</v>
+        <v>130300987</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490688</v>
+        <v>490657</v>
       </c>
       <c r="R30" t="n">
-        <v>6687940</v>
+        <v>6687863</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4546,45 +4546,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300845</v>
+        <v>130300089</v>
       </c>
       <c r="B37" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490638</v>
+        <v>490754</v>
       </c>
       <c r="R37" t="n">
-        <v>6687897</v>
+        <v>6687921</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,45 +4653,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300674</v>
+        <v>130298958</v>
       </c>
       <c r="B38" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490640</v>
+        <v>490730</v>
       </c>
       <c r="R38" t="n">
-        <v>6687937</v>
+        <v>6687864</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300601</v>
+        <v>130299047</v>
       </c>
       <c r="B39" t="n">
         <v>98957</v>
@@ -4791,14 +4791,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490648</v>
+        <v>490706</v>
       </c>
       <c r="R39" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,32 +4867,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130298958</v>
+        <v>130299645</v>
       </c>
       <c r="B40" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490730</v>
+        <v>490670</v>
       </c>
       <c r="R40" t="n">
-        <v>6687864</v>
+        <v>6687843</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,45 +4974,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300089</v>
+        <v>130300845</v>
       </c>
       <c r="B41" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490754</v>
+        <v>490638</v>
       </c>
       <c r="R41" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,7 +5081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299645</v>
+        <v>130300674</v>
       </c>
       <c r="B42" t="n">
         <v>98957</v>
@@ -5112,14 +5112,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490670</v>
+        <v>490640</v>
       </c>
       <c r="R42" t="n">
-        <v>6687843</v>
+        <v>6687937</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,7 +5188,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130299047</v>
+        <v>130300601</v>
       </c>
       <c r="B43" t="n">
         <v>98957</v>
@@ -5219,14 +5219,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490706</v>
+        <v>490648</v>
       </c>
       <c r="R43" t="n">
-        <v>6687897</v>
+        <v>6687935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,7 +5295,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299949</v>
+        <v>130298757</v>
       </c>
       <c r="B44" t="n">
         <v>98957</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490740</v>
+        <v>490809</v>
       </c>
       <c r="R44" t="n">
-        <v>6687892</v>
+        <v>6687859</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,7 +5402,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130298688</v>
+        <v>130299949</v>
       </c>
       <c r="B45" t="n">
         <v>98957</v>
@@ -5430,31 +5430,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490823</v>
+        <v>490740</v>
       </c>
       <c r="R45" t="n">
-        <v>6687809</v>
+        <v>6687892</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5486,7 +5472,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5496,12 +5482,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5528,7 +5509,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298757</v>
+        <v>130298688</v>
       </c>
       <c r="B46" t="n">
         <v>98957</v>
@@ -5556,17 +5537,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490809</v>
+        <v>490823</v>
       </c>
       <c r="R46" t="n">
-        <v>6687859</v>
+        <v>6687809</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5598,7 +5593,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5608,7 +5603,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5864,45 +5864,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130300215</v>
+        <v>130299179</v>
       </c>
       <c r="B49" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490750</v>
+        <v>490663</v>
       </c>
       <c r="R49" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5934,7 +5939,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5944,7 +5949,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5971,50 +5981,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299179</v>
+        <v>130299662</v>
       </c>
       <c r="B50" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490663</v>
+        <v>490664</v>
       </c>
       <c r="R50" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6046,7 +6051,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6056,12 +6061,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299662</v>
+        <v>130300215</v>
       </c>
       <c r="B52" t="n">
         <v>98957</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490664</v>
+        <v>490750</v>
       </c>
       <c r="R52" t="n">
-        <v>6687847</v>
+        <v>6687940</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6642,45 +6642,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130300918</v>
+        <v>130299999</v>
       </c>
       <c r="B56" t="n">
-        <v>97203</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490628</v>
+        <v>490742</v>
       </c>
       <c r="R56" t="n">
-        <v>6687894</v>
+        <v>6687893</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,45 +6754,59 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299909</v>
+        <v>130298364</v>
       </c>
       <c r="B57" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490723</v>
+        <v>490775</v>
       </c>
       <c r="R57" t="n">
-        <v>6687910</v>
+        <v>6687939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6819,7 +6838,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6829,7 +6848,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6856,54 +6875,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299604</v>
+        <v>130300918</v>
       </c>
       <c r="B58" t="n">
-        <v>93047</v>
+        <v>97203</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490666</v>
+        <v>490628</v>
       </c>
       <c r="R58" t="n">
-        <v>6687830</v>
+        <v>6687894</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6945,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6955,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,47 +6982,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130298364</v>
+        <v>130299604</v>
       </c>
       <c r="B59" t="n">
-        <v>98957</v>
+        <v>93047</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7021,10 +7026,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490775</v>
+        <v>490666</v>
       </c>
       <c r="R59" t="n">
-        <v>6687939</v>
+        <v>6687830</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7066,7 +7071,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7093,32 +7098,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299214</v>
+        <v>130299909</v>
       </c>
       <c r="B60" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490665</v>
+        <v>490723</v>
       </c>
       <c r="R60" t="n">
-        <v>6687861</v>
+        <v>6687910</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7163,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7173,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7200,50 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299999</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>98957</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490742</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687893</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130300998</v>
       </c>
       <c r="B3" t="n">
         <v>98957</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490659</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130300930</v>
       </c>
       <c r="B4" t="n">
         <v>98957</v>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490628</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687894</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130300146</v>
       </c>
       <c r="B5" t="n">
         <v>98957</v>
@@ -1037,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490771</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130298671</v>
       </c>
       <c r="B6" t="n">
         <v>98957</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490825</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
         <v>98957</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
         <v>98957</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,45 +1755,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298423</v>
+        <v>130300768</v>
       </c>
       <c r="B12" t="n">
-        <v>92220</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490629</v>
       </c>
       <c r="R12" t="n">
-        <v>6687879</v>
+        <v>6687910</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298782</v>
+        <v>130298423</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>92220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,48 +1878,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490803</v>
+        <v>490832</v>
       </c>
       <c r="R13" t="n">
-        <v>6687883</v>
+        <v>6687879</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,50 +2193,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490803</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,45 +2528,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299218</v>
+        <v>130299657</v>
       </c>
       <c r="B19" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490666</v>
+        <v>490669</v>
       </c>
       <c r="R19" t="n">
-        <v>6687855</v>
+        <v>6687844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2613,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,7 +2645,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298529</v>
+        <v>130299218</v>
       </c>
       <c r="B20" t="n">
         <v>98957</v>
@@ -2663,31 +2673,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490885</v>
+        <v>490666</v>
       </c>
       <c r="R20" t="n">
-        <v>6687821</v>
+        <v>6687855</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2725,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,7 +2752,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298375</v>
+        <v>130298529</v>
       </c>
       <c r="B21" t="n">
         <v>98957</v>
@@ -2786,17 +2782,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490885</v>
       </c>
       <c r="R21" t="n">
-        <v>6687911</v>
+        <v>6687821</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,38 +2873,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130299657</v>
+        <v>130298375</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490669</v>
+        <v>490816</v>
       </c>
       <c r="R22" t="n">
-        <v>6687844</v>
+        <v>6687911</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2967,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,50 +3106,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300626</v>
+        <v>130298467</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490855</v>
       </c>
       <c r="R24" t="n">
-        <v>6687936</v>
+        <v>6687847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3181,7 +3176,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3186,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,45 +3213,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130298467</v>
+        <v>130300626</v>
       </c>
       <c r="B25" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490855</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>6687847</v>
+        <v>6687936</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B26" t="n">
-        <v>91761</v>
+        <v>81196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R26" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130299399</v>
+        <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>81196</v>
+        <v>91761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490680</v>
+        <v>490831</v>
       </c>
       <c r="R27" t="n">
-        <v>6687839</v>
+        <v>6687885</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,38 +3651,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300532</v>
+        <v>130299013</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>98957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490688</v>
+        <v>490722</v>
       </c>
       <c r="R29" t="n">
-        <v>6687940</v>
+        <v>6687888</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3735,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3745,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Urholkad märg.</t>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4313,47 +4322,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299013</v>
+        <v>130300532</v>
       </c>
       <c r="B35" t="n">
-        <v>98957</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490722</v>
+        <v>490688</v>
       </c>
       <c r="R35" t="n">
-        <v>6687888</v>
+        <v>6687940</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300089</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
         <v>97203</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490754</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687921</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130298958</v>
+        <v>130300089</v>
       </c>
       <c r="B38" t="n">
         <v>97203</v>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490730</v>
+        <v>490754</v>
       </c>
       <c r="R38" t="n">
-        <v>6687864</v>
+        <v>6687921</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130299047</v>
+        <v>130300845</v>
       </c>
       <c r="B39" t="n">
         <v>98957</v>
@@ -4791,11 +4791,11 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490706</v>
+        <v>490638</v>
       </c>
       <c r="R39" t="n">
         <v>6687897</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130299645</v>
+        <v>130300674</v>
       </c>
       <c r="B40" t="n">
         <v>98957</v>
@@ -4898,14 +4898,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490670</v>
+        <v>490640</v>
       </c>
       <c r="R40" t="n">
-        <v>6687843</v>
+        <v>6687937</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300845</v>
+        <v>130300601</v>
       </c>
       <c r="B41" t="n">
         <v>98957</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490638</v>
+        <v>490648</v>
       </c>
       <c r="R41" t="n">
-        <v>6687897</v>
+        <v>6687935</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,7 +5081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300674</v>
+        <v>130299645</v>
       </c>
       <c r="B42" t="n">
         <v>98957</v>
@@ -5112,14 +5112,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490640</v>
+        <v>490670</v>
       </c>
       <c r="R42" t="n">
-        <v>6687937</v>
+        <v>6687843</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,7 +5188,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130300601</v>
+        <v>130299047</v>
       </c>
       <c r="B43" t="n">
         <v>98957</v>
@@ -5219,14 +5219,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490648</v>
+        <v>490706</v>
       </c>
       <c r="R43" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,45 +5295,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130298757</v>
+        <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490809</v>
+        <v>490689</v>
       </c>
       <c r="R44" t="n">
-        <v>6687859</v>
+        <v>6687918</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5365,7 +5370,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5375,7 +5380,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5635,50 +5645,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130299124</v>
+        <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490689</v>
+        <v>490809</v>
       </c>
       <c r="R47" t="n">
-        <v>6687918</v>
+        <v>6687859</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,7 +5715,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5720,12 +5725,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,50 +5752,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R48" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,7 +5832,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5864,10 +5859,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299179</v>
+        <v>130299101</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5875,16 +5870,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5904,10 +5899,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490663</v>
+        <v>490685</v>
       </c>
       <c r="R49" t="n">
-        <v>6687895</v>
+        <v>6687923</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,12 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,45 +5971,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299662</v>
+        <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490664</v>
+        <v>490663</v>
       </c>
       <c r="R50" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6051,7 +6046,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6061,7 +6056,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
         <v>98957</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6642,50 +6642,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299999</v>
+        <v>130300918</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>97203</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490742</v>
+        <v>490628</v>
       </c>
       <c r="R56" t="n">
-        <v>6687893</v>
+        <v>6687894</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6727,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,45 +6870,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130299214</v>
       </c>
       <c r="B58" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490665</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687861</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,7 +6940,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6955,7 +6950,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6982,54 +6977,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299604</v>
+        <v>130299909</v>
       </c>
       <c r="B59" t="n">
-        <v>93047</v>
+        <v>97203</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490666</v>
+        <v>490723</v>
       </c>
       <c r="R59" t="n">
-        <v>6687830</v>
+        <v>6687910</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7061,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7071,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7098,45 +7084,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299909</v>
+        <v>130299604</v>
       </c>
       <c r="B60" t="n">
-        <v>97203</v>
+        <v>93047</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490723</v>
+        <v>490666</v>
       </c>
       <c r="R60" t="n">
-        <v>6687910</v>
+        <v>6687830</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7163,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7173,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7200,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130299999</v>
       </c>
       <c r="B61" t="n">
-        <v>98957</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490742</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687893</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130298671</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490825</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687809</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300998</v>
+        <v>130299512</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490659</v>
+        <v>490708</v>
       </c>
       <c r="R3" t="n">
-        <v>6687865</v>
+        <v>6687780</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300930</v>
+        <v>130300998</v>
       </c>
       <c r="B4" t="n">
         <v>98957</v>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490628</v>
+        <v>490659</v>
       </c>
       <c r="R4" t="n">
-        <v>6687894</v>
+        <v>6687865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300146</v>
+        <v>130300930</v>
       </c>
       <c r="B5" t="n">
         <v>98957</v>
@@ -1037,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490771</v>
+        <v>490628</v>
       </c>
       <c r="R5" t="n">
-        <v>6687913</v>
+        <v>6687894</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298671</v>
+        <v>130300146</v>
       </c>
       <c r="B6" t="n">
         <v>98957</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490825</v>
+        <v>490771</v>
       </c>
       <c r="R6" t="n">
-        <v>6687809</v>
+        <v>6687913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1755,50 +1755,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130300768</v>
+        <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>92220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490629</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6687910</v>
+        <v>6687879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298423</v>
+        <v>130299757</v>
       </c>
       <c r="B13" t="n">
-        <v>92220</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490832</v>
+        <v>490654</v>
       </c>
       <c r="R13" t="n">
-        <v>6687879</v>
+        <v>6687872</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130299757</v>
+        <v>130298405</v>
       </c>
       <c r="B14" t="n">
         <v>98957</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490654</v>
+        <v>490825</v>
       </c>
       <c r="R14" t="n">
-        <v>6687872</v>
+        <v>6687878</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B15" t="n">
         <v>98957</v>
@@ -2114,17 +2109,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R15" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,59 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,38 +2528,47 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299657</v>
+        <v>130298529</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2568,10 +2577,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490669</v>
+        <v>490885</v>
       </c>
       <c r="R19" t="n">
-        <v>6687844</v>
+        <v>6687821</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2612,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2622,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,45 +2649,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299218</v>
+        <v>130299657</v>
       </c>
       <c r="B20" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490666</v>
+        <v>490669</v>
       </c>
       <c r="R20" t="n">
-        <v>6687855</v>
+        <v>6687844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2724,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2734,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,7 +2766,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298529</v>
+        <v>130299218</v>
       </c>
       <c r="B21" t="n">
         <v>98957</v>
@@ -2780,31 +2794,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490885</v>
+        <v>490666</v>
       </c>
       <c r="R21" t="n">
-        <v>6687821</v>
+        <v>6687855</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490855</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3074,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,45 +3101,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B24" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R24" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3176,7 +3171,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3186,7 +3181,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130299399</v>
+        <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>81196</v>
+        <v>91761</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490680</v>
+        <v>490831</v>
       </c>
       <c r="R26" t="n">
-        <v>6687839</v>
+        <v>6687885</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>91761</v>
+        <v>81196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R27" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,47 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130299013</v>
+        <v>130299432</v>
       </c>
       <c r="B29" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3700,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490722</v>
+        <v>490697</v>
       </c>
       <c r="R29" t="n">
-        <v>6687888</v>
+        <v>6687828</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3735,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3745,12 +3736,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,50 +3763,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300987</v>
+        <v>130299120</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490657</v>
+        <v>490690</v>
       </c>
       <c r="R30" t="n">
-        <v>6687863</v>
+        <v>6687921</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3852,7 +3833,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3862,7 +3843,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,50 +3870,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130299432</v>
+        <v>130298471</v>
       </c>
       <c r="B31" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490697</v>
+        <v>490854</v>
       </c>
       <c r="R31" t="n">
-        <v>6687828</v>
+        <v>6687846</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3964,7 +3940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3974,7 +3950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,7 +3977,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130298471</v>
+        <v>130299915</v>
       </c>
       <c r="B32" t="n">
         <v>98957</v>
@@ -4036,10 +4012,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490854</v>
+        <v>490724</v>
       </c>
       <c r="R32" t="n">
-        <v>6687846</v>
+        <v>6687908</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4071,7 +4047,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,7 +4057,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4108,7 +4084,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299120</v>
+        <v>130299013</v>
       </c>
       <c r="B33" t="n">
         <v>98957</v>
@@ -4136,17 +4112,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490690</v>
+        <v>490722</v>
       </c>
       <c r="R33" t="n">
-        <v>6687921</v>
+        <v>6687888</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4178,7 +4168,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4188,7 +4178,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4215,45 +4210,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299915</v>
+        <v>130300987</v>
       </c>
       <c r="B34" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490724</v>
+        <v>490657</v>
       </c>
       <c r="R34" t="n">
-        <v>6687908</v>
+        <v>6687863</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B37" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300845</v>
+        <v>130300674</v>
       </c>
       <c r="B39" t="n">
         <v>98957</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490638</v>
+        <v>490640</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687937</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300674</v>
+        <v>130300601</v>
       </c>
       <c r="B40" t="n">
         <v>98957</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490640</v>
+        <v>490648</v>
       </c>
       <c r="R40" t="n">
-        <v>6687937</v>
+        <v>6687935</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300601</v>
+        <v>130300845</v>
       </c>
       <c r="B41" t="n">
         <v>98957</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490648</v>
+        <v>490638</v>
       </c>
       <c r="R41" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B43" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R43" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,50 +5295,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299124</v>
+        <v>130299949</v>
       </c>
       <c r="B44" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490689</v>
+        <v>490740</v>
       </c>
       <c r="R44" t="n">
-        <v>6687918</v>
+        <v>6687892</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5370,7 +5365,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5380,12 +5375,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,7 +5402,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130299949</v>
+        <v>130298688</v>
       </c>
       <c r="B45" t="n">
         <v>98957</v>
@@ -5440,17 +5430,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490740</v>
+        <v>490823</v>
       </c>
       <c r="R45" t="n">
-        <v>6687892</v>
+        <v>6687809</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5482,7 +5486,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5492,7 +5496,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5519,7 +5528,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298688</v>
+        <v>130298757</v>
       </c>
       <c r="B46" t="n">
         <v>98957</v>
@@ -5547,31 +5556,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490823</v>
+        <v>490809</v>
       </c>
       <c r="R46" t="n">
-        <v>6687809</v>
+        <v>6687859</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5603,7 +5598,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5613,12 +5608,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,45 +5635,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130298757</v>
+        <v>130299124</v>
       </c>
       <c r="B47" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490809</v>
+        <v>490689</v>
       </c>
       <c r="R47" t="n">
-        <v>6687859</v>
+        <v>6687918</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5715,7 +5710,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5725,7 +5720,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,45 +5752,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130300215</v>
+        <v>130299179</v>
       </c>
       <c r="B48" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490750</v>
+        <v>490663</v>
       </c>
       <c r="R48" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5832,7 +5837,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5971,38 +5981,47 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299179</v>
+        <v>130298812</v>
       </c>
       <c r="B50" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6011,7 +6030,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490663</v>
+        <v>490761</v>
       </c>
       <c r="R50" t="n">
         <v>6687895</v>
@@ -6046,7 +6065,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6056,12 +6075,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6088,7 +6107,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130298812</v>
+        <v>130299662</v>
       </c>
       <c r="B51" t="n">
         <v>98957</v>
@@ -6116,31 +6135,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490761</v>
+        <v>490664</v>
       </c>
       <c r="R51" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6172,7 +6177,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6182,12 +6187,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299662</v>
+        <v>130300215</v>
       </c>
       <c r="B52" t="n">
         <v>98957</v>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490664</v>
+        <v>490750</v>
       </c>
       <c r="R52" t="n">
-        <v>6687847</v>
+        <v>6687940</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6749,59 +6749,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130298364</v>
+        <v>130299909</v>
       </c>
       <c r="B57" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490775</v>
+        <v>490723</v>
       </c>
       <c r="R57" t="n">
-        <v>6687939</v>
+        <v>6687910</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6833,7 +6819,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6843,7 +6829,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6870,45 +6856,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299214</v>
+        <v>130299604</v>
       </c>
       <c r="B58" t="n">
-        <v>98957</v>
+        <v>93047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490665</v>
+        <v>490666</v>
       </c>
       <c r="R58" t="n">
-        <v>6687861</v>
+        <v>6687830</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,45 +6972,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299909</v>
+        <v>130299999</v>
       </c>
       <c r="B59" t="n">
-        <v>97203</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490723</v>
+        <v>490742</v>
       </c>
       <c r="R59" t="n">
-        <v>6687910</v>
+        <v>6687893</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,42 +7084,47 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299604</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>93047</v>
+        <v>98957</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490666</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687830</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7163,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7173,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7200,50 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299999</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>98957</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490742</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687893</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130298671</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490825</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687809</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130299512</v>
+        <v>130298671</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>98970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490708</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6687780</v>
+        <v>6687809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>130300998</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130300930</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298423</v>
+        <v>130299757</v>
       </c>
       <c r="B12" t="n">
-        <v>92220</v>
+        <v>98970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490654</v>
       </c>
       <c r="R12" t="n">
-        <v>6687879</v>
+        <v>6687872</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130299757</v>
+        <v>130298405</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490654</v>
+        <v>490825</v>
       </c>
       <c r="R13" t="n">
-        <v>6687872</v>
+        <v>6687878</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B14" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,17 +2002,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R14" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,59 +2095,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B15" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R15" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,50 +2207,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130298423</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>92233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490832</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687879</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2317,7 @@
         <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,47 +2528,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298529</v>
+        <v>130299657</v>
       </c>
       <c r="B19" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2577,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490885</v>
+        <v>490669</v>
       </c>
       <c r="R19" t="n">
-        <v>6687821</v>
+        <v>6687844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2612,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2613,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,50 +2645,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299657</v>
+        <v>130299218</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490669</v>
+        <v>490666</v>
       </c>
       <c r="R20" t="n">
-        <v>6687844</v>
+        <v>6687855</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2724,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2734,12 +2725,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130299218</v>
+        <v>130298529</v>
       </c>
       <c r="B21" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,17 +2780,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490666</v>
+        <v>490885</v>
       </c>
       <c r="R21" t="n">
-        <v>6687855</v>
+        <v>6687821</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,7 +2876,7 @@
         <v>130298375</v>
       </c>
       <c r="B22" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R23" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,7 +3074,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>57862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,16 +3117,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3130,16 +3135,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3171,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3181,12 +3191,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,50 +3223,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300626</v>
+        <v>130298467</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>98970</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490855</v>
       </c>
       <c r="R25" t="n">
-        <v>6687936</v>
+        <v>6687847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3303,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,7 +3333,7 @@
         <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>81196</v>
+        <v>81204</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>130300054</v>
       </c>
       <c r="B28" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>130299432</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299120</v>
+        <v>130299915</v>
       </c>
       <c r="B30" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490690</v>
+        <v>490724</v>
       </c>
       <c r="R30" t="n">
-        <v>6687921</v>
+        <v>6687908</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3870,45 +3870,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130300987</v>
       </c>
       <c r="B31" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490657</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687863</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3940,7 +3945,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3950,7 +3955,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3977,45 +3982,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299915</v>
+        <v>130300532</v>
       </c>
       <c r="B32" t="n">
-        <v>98957</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490724</v>
+        <v>490688</v>
       </c>
       <c r="R32" t="n">
-        <v>6687908</v>
+        <v>6687940</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4047,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4057,7 +4067,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,10 +4099,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299013</v>
+        <v>130298471</v>
       </c>
       <c r="B33" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,31 +4127,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490722</v>
+        <v>490854</v>
       </c>
       <c r="R33" t="n">
-        <v>6687888</v>
+        <v>6687846</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4168,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4178,12 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,50 +4206,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300987</v>
+        <v>130299120</v>
       </c>
       <c r="B34" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490657</v>
+        <v>490690</v>
       </c>
       <c r="R34" t="n">
-        <v>6687863</v>
+        <v>6687921</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,38 +4313,47 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300532</v>
+        <v>130299013</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>98970</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490688</v>
+        <v>490722</v>
       </c>
       <c r="R35" t="n">
-        <v>6687940</v>
+        <v>6687888</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Urholkad märg.</t>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130299047</v>
+        <v>130300089</v>
       </c>
       <c r="B37" t="n">
-        <v>98957</v>
+        <v>97216</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490706</v>
+        <v>490754</v>
       </c>
       <c r="R37" t="n">
-        <v>6687897</v>
+        <v>6687921</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,45 +4653,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300089</v>
+        <v>130300845</v>
       </c>
       <c r="B38" t="n">
-        <v>97203</v>
+        <v>98970</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490754</v>
+        <v>490638</v>
       </c>
       <c r="R38" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,7 +4763,7 @@
         <v>130300674</v>
       </c>
       <c r="B39" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>130300601</v>
       </c>
       <c r="B40" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300845</v>
+        <v>130299645</v>
       </c>
       <c r="B41" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5005,14 +5005,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490638</v>
+        <v>490670</v>
       </c>
       <c r="R41" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299645</v>
+        <v>130299047</v>
       </c>
       <c r="B42" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490670</v>
+        <v>490706</v>
       </c>
       <c r="R42" t="n">
-        <v>6687843</v>
+        <v>6687897</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,7 +5191,7 @@
         <v>130298958</v>
       </c>
       <c r="B43" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5295,45 +5295,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299949</v>
+        <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490740</v>
+        <v>490689</v>
       </c>
       <c r="R44" t="n">
-        <v>6687892</v>
+        <v>6687918</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5365,7 +5370,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5375,7 +5380,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,10 +5412,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130298688</v>
+        <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5430,31 +5440,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490823</v>
+        <v>490740</v>
       </c>
       <c r="R45" t="n">
-        <v>6687809</v>
+        <v>6687892</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5486,7 +5482,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5496,12 +5492,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5528,10 +5519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298757</v>
+        <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5556,17 +5547,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490809</v>
+        <v>490823</v>
       </c>
       <c r="R46" t="n">
-        <v>6687859</v>
+        <v>6687809</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5598,7 +5603,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5608,7 +5613,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5635,50 +5645,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130299124</v>
+        <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490689</v>
+        <v>490809</v>
       </c>
       <c r="R47" t="n">
-        <v>6687918</v>
+        <v>6687859</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,7 +5715,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5720,12 +5725,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,7 +5755,7 @@
         <v>130299179</v>
       </c>
       <c r="B48" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5869,50 +5869,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299101</v>
+        <v>130300215</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490685</v>
+        <v>490750</v>
       </c>
       <c r="R49" t="n">
-        <v>6687923</v>
+        <v>6687940</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5944,7 +5939,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5954,7 +5949,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,47 +5976,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130298812</v>
+        <v>130299101</v>
       </c>
       <c r="B50" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6030,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490761</v>
+        <v>490685</v>
       </c>
       <c r="R50" t="n">
-        <v>6687895</v>
+        <v>6687923</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6051,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6075,12 +6061,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130299662</v>
+        <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,17 +6116,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490664</v>
+        <v>490761</v>
       </c>
       <c r="R51" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6177,7 +6172,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6187,7 +6182,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490664</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6324,7 +6324,7 @@
         <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6642,45 +6642,59 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130300918</v>
+        <v>130298364</v>
       </c>
       <c r="B56" t="n">
-        <v>97203</v>
+        <v>98970</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490628</v>
+        <v>490775</v>
       </c>
       <c r="R56" t="n">
-        <v>6687894</v>
+        <v>6687939</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6726,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6736,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,32 +6763,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299909</v>
+        <v>130299214</v>
       </c>
       <c r="B57" t="n">
-        <v>97203</v>
+        <v>98970</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6784,10 +6798,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490723</v>
+        <v>490665</v>
       </c>
       <c r="R57" t="n">
-        <v>6687910</v>
+        <v>6687861</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6819,7 +6833,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6829,7 +6843,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6856,54 +6870,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299604</v>
+        <v>130299909</v>
       </c>
       <c r="B58" t="n">
-        <v>93047</v>
+        <v>97216</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490666</v>
+        <v>490723</v>
       </c>
       <c r="R58" t="n">
-        <v>6687830</v>
+        <v>6687910</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6940,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6950,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,10 +6977,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130299604</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>93060</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6983,27 +6988,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7012,10 +7021,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490666</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687830</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7056,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7066,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,47 +7093,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130299999</v>
       </c>
       <c r="B60" t="n">
-        <v>98957</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490742</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687893</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130300918</v>
       </c>
       <c r="B61" t="n">
-        <v>98957</v>
+        <v>97216</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490628</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687894</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130300998</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>98971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490659</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130300930</v>
       </c>
       <c r="B3" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490628</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130300146</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490771</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130299512</v>
       </c>
       <c r="B5" t="n">
-        <v>98970</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490708</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687780</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130298671</v>
       </c>
       <c r="B6" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490825</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298552</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490897</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687798</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130299757</v>
+        <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>98970</v>
+        <v>92234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490654</v>
+        <v>490832</v>
       </c>
       <c r="R12" t="n">
-        <v>6687872</v>
+        <v>6687879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130298405</v>
+        <v>130300768</v>
       </c>
       <c r="B13" t="n">
-        <v>98970</v>
+        <v>57860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490825</v>
+        <v>490629</v>
       </c>
       <c r="R13" t="n">
-        <v>6687878</v>
+        <v>6687910</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298782</v>
+        <v>130299757</v>
       </c>
       <c r="B14" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,31 +2002,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490803</v>
+        <v>490654</v>
       </c>
       <c r="R14" t="n">
-        <v>6687883</v>
+        <v>6687872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,50 +2086,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130300768</v>
+        <v>130298405</v>
       </c>
       <c r="B15" t="n">
-        <v>57859</v>
+        <v>98971</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490629</v>
+        <v>490825</v>
       </c>
       <c r="R15" t="n">
-        <v>6687910</v>
+        <v>6687878</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298423</v>
+        <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>98971</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2204,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490832</v>
+        <v>490803</v>
       </c>
       <c r="R16" t="n">
-        <v>6687879</v>
+        <v>6687883</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,7 +2317,7 @@
         <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>92072</v>
+        <v>92073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,50 +2528,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299657</v>
+        <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>57859</v>
+        <v>98971</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490669</v>
+        <v>490666</v>
       </c>
       <c r="R19" t="n">
-        <v>6687844</v>
+        <v>6687855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299218</v>
+        <v>130298529</v>
       </c>
       <c r="B20" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,17 +2663,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490666</v>
+        <v>490885</v>
       </c>
       <c r="R20" t="n">
-        <v>6687855</v>
+        <v>6687821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298529</v>
+        <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,17 +2786,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2801,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490885</v>
+        <v>490816</v>
       </c>
       <c r="R21" t="n">
-        <v>6687821</v>
+        <v>6687911</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,47 +2877,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130298375</v>
+        <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>98970</v>
+        <v>57860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490816</v>
+        <v>490669</v>
       </c>
       <c r="R22" t="n">
-        <v>6687911</v>
+        <v>6687844</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2967,7 +2962,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,7 +2997,7 @@
         <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>130298467</v>
       </c>
       <c r="B25" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>81204</v>
+        <v>81205</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>130300054</v>
       </c>
       <c r="B28" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130299432</v>
+        <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490697</v>
+        <v>490657</v>
       </c>
       <c r="R29" t="n">
-        <v>6687828</v>
+        <v>6687863</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,45 +3763,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299915</v>
+        <v>130299432</v>
       </c>
       <c r="B30" t="n">
-        <v>98970</v>
+        <v>57860</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490724</v>
+        <v>490697</v>
       </c>
       <c r="R30" t="n">
-        <v>6687908</v>
+        <v>6687828</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3833,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3843,7 +3848,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3870,50 +3875,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130300987</v>
+        <v>130298471</v>
       </c>
       <c r="B31" t="n">
-        <v>57859</v>
+        <v>98971</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490657</v>
+        <v>490854</v>
       </c>
       <c r="R31" t="n">
-        <v>6687863</v>
+        <v>6687846</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,50 +3982,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130300532</v>
+        <v>130299120</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>98971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490688</v>
+        <v>490690</v>
       </c>
       <c r="R32" t="n">
-        <v>6687940</v>
+        <v>6687921</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4057,7 +4052,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4062,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4099,10 +4089,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130298471</v>
+        <v>130299915</v>
       </c>
       <c r="B33" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,10 +4124,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490854</v>
+        <v>490724</v>
       </c>
       <c r="R33" t="n">
-        <v>6687846</v>
+        <v>6687908</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4169,7 +4159,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4169,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4206,10 +4196,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299120</v>
+        <v>130299013</v>
       </c>
       <c r="B34" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,17 +4224,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490690</v>
+        <v>490722</v>
       </c>
       <c r="R34" t="n">
-        <v>6687921</v>
+        <v>6687888</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4276,7 +4280,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4286,7 +4290,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,47 +4322,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299013</v>
+        <v>130300532</v>
       </c>
       <c r="B35" t="n">
-        <v>98970</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490722</v>
+        <v>490688</v>
       </c>
       <c r="R35" t="n">
-        <v>6687888</v>
+        <v>6687940</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>130300089</v>
       </c>
       <c r="B37" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>130300845</v>
       </c>
       <c r="B38" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>130300674</v>
       </c>
       <c r="B39" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>130300601</v>
       </c>
       <c r="B40" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4974,32 +4974,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130299645</v>
+        <v>130298958</v>
       </c>
       <c r="B41" t="n">
-        <v>98970</v>
+        <v>97217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490670</v>
+        <v>490730</v>
       </c>
       <c r="R41" t="n">
-        <v>6687843</v>
+        <v>6687864</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299047</v>
+        <v>130299645</v>
       </c>
       <c r="B42" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490706</v>
+        <v>490670</v>
       </c>
       <c r="R42" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130298958</v>
+        <v>130299047</v>
       </c>
       <c r="B43" t="n">
-        <v>97216</v>
+        <v>98971</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490730</v>
+        <v>490706</v>
       </c>
       <c r="R43" t="n">
-        <v>6687864</v>
+        <v>6687897</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,7 +5298,7 @@
         <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>130299949</v>
       </c>
       <c r="B45" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130298688</v>
       </c>
       <c r="B46" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>130298757</v>
       </c>
       <c r="B47" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,50 +5752,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299179</v>
+        <v>130300215</v>
       </c>
       <c r="B48" t="n">
-        <v>57862</v>
+        <v>98971</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490663</v>
+        <v>490750</v>
       </c>
       <c r="R48" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,12 +5832,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5869,45 +5859,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130300215</v>
+        <v>130299101</v>
       </c>
       <c r="B49" t="n">
-        <v>98970</v>
+        <v>57860</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490750</v>
+        <v>490685</v>
       </c>
       <c r="R49" t="n">
-        <v>6687940</v>
+        <v>6687923</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,7 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5976,10 +5971,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299101</v>
+        <v>130299179</v>
       </c>
       <c r="B50" t="n">
-        <v>57859</v>
+        <v>57863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,16 +5982,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,10 +6011,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490685</v>
+        <v>490663</v>
       </c>
       <c r="R50" t="n">
-        <v>6687923</v>
+        <v>6687895</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6051,7 +6046,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6061,7 +6056,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6091,7 +6091,7 @@
         <v>130298812</v>
       </c>
       <c r="B51" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>130299662</v>
       </c>
       <c r="B52" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6642,47 +6642,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130298364</v>
+        <v>130299604</v>
       </c>
       <c r="B56" t="n">
-        <v>98970</v>
+        <v>93061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6686,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490775</v>
+        <v>490666</v>
       </c>
       <c r="R56" t="n">
-        <v>6687939</v>
+        <v>6687830</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6726,7 +6721,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6736,7 +6731,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6763,32 +6758,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299214</v>
+        <v>130299909</v>
       </c>
       <c r="B57" t="n">
-        <v>98970</v>
+        <v>97217</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6798,10 +6793,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490665</v>
+        <v>490723</v>
       </c>
       <c r="R57" t="n">
-        <v>6687861</v>
+        <v>6687910</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6833,7 +6828,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6843,7 +6838,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6870,10 +6865,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299909</v>
+        <v>130300918</v>
       </c>
       <c r="B58" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,14 +6896,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490723</v>
+        <v>490628</v>
       </c>
       <c r="R58" t="n">
-        <v>6687910</v>
+        <v>6687894</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6940,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6950,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,42 +6972,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299604</v>
+        <v>130298364</v>
       </c>
       <c r="B59" t="n">
-        <v>93060</v>
+        <v>98971</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490666</v>
+        <v>490775</v>
       </c>
       <c r="R59" t="n">
-        <v>6687830</v>
+        <v>6687939</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7093,50 +7093,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299999</v>
+        <v>130299214</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>98971</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490742</v>
+        <v>490665</v>
       </c>
       <c r="R60" t="n">
-        <v>6687893</v>
+        <v>6687861</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7163,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7173,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,45 +7200,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130300918</v>
+        <v>130299999</v>
       </c>
       <c r="B61" t="n">
-        <v>97216</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490628</v>
+        <v>490742</v>
       </c>
       <c r="R61" t="n">
-        <v>6687894</v>
+        <v>6687893</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130300998</v>
+        <v>130298671</v>
       </c>
       <c r="B2" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490659</v>
+        <v>490825</v>
       </c>
       <c r="R2" t="n">
-        <v>6687865</v>
+        <v>6687809</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300930</v>
+        <v>130299512</v>
       </c>
       <c r="B3" t="n">
-        <v>98971</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490628</v>
+        <v>490708</v>
       </c>
       <c r="R3" t="n">
-        <v>6687894</v>
+        <v>6687780</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300146</v>
+        <v>130300998</v>
       </c>
       <c r="B4" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490771</v>
+        <v>490659</v>
       </c>
       <c r="R4" t="n">
-        <v>6687913</v>
+        <v>6687865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130299512</v>
+        <v>130300930</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490708</v>
+        <v>490628</v>
       </c>
       <c r="R5" t="n">
-        <v>6687780</v>
+        <v>6687894</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298671</v>
+        <v>130300146</v>
       </c>
       <c r="B6" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490825</v>
+        <v>490771</v>
       </c>
       <c r="R6" t="n">
-        <v>6687809</v>
+        <v>6687913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130299032</v>
       </c>
       <c r="B7" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130300120</v>
       </c>
       <c r="B8" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490773</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687906</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130298856</v>
       </c>
       <c r="B9" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490770</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687828</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298552</v>
       </c>
       <c r="B10" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490897</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687798</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130299228</v>
       </c>
       <c r="B11" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130298423</v>
       </c>
       <c r="B12" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>130300768</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>130299757</v>
       </c>
       <c r="B14" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>130298405</v>
       </c>
       <c r="B15" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>130298782</v>
       </c>
       <c r="B16" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,32 +2314,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130298439</v>
+        <v>130299411</v>
       </c>
       <c r="B17" t="n">
-        <v>92073</v>
+        <v>98974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490826</v>
+        <v>490679</v>
       </c>
       <c r="R17" t="n">
-        <v>6687871</v>
+        <v>6687837</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130299411</v>
+        <v>130298439</v>
       </c>
       <c r="B18" t="n">
-        <v>98971</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490679</v>
+        <v>490826</v>
       </c>
       <c r="R18" t="n">
-        <v>6687837</v>
+        <v>6687871</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,45 +2528,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299218</v>
+        <v>130299657</v>
       </c>
       <c r="B19" t="n">
-        <v>98971</v>
+        <v>57861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490666</v>
+        <v>490669</v>
       </c>
       <c r="R19" t="n">
-        <v>6687855</v>
+        <v>6687844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2613,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298529</v>
+        <v>130299218</v>
       </c>
       <c r="B20" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,31 +2673,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490885</v>
+        <v>490666</v>
       </c>
       <c r="R20" t="n">
-        <v>6687821</v>
+        <v>6687855</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2725,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2759,7 +2755,7 @@
         <v>130298375</v>
       </c>
       <c r="B21" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,38 +2873,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130299657</v>
+        <v>130298529</v>
       </c>
       <c r="B22" t="n">
-        <v>57860</v>
+        <v>98974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490669</v>
+        <v>490885</v>
       </c>
       <c r="R22" t="n">
-        <v>6687844</v>
+        <v>6687821</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2967,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130298467</v>
       </c>
       <c r="B23" t="n">
-        <v>57860</v>
+        <v>98974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490855</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3074,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,7 +3104,7 @@
         <v>130300626</v>
       </c>
       <c r="B24" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,45 +3218,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B25" t="n">
-        <v>98971</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R25" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130298421</v>
+        <v>130300054</v>
       </c>
       <c r="B26" t="n">
-        <v>91775</v>
+        <v>97220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490831</v>
+        <v>490743</v>
       </c>
       <c r="R26" t="n">
-        <v>6687885</v>
+        <v>6687908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130299399</v>
+        <v>130298421</v>
       </c>
       <c r="B27" t="n">
-        <v>81205</v>
+        <v>91776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490680</v>
+        <v>490831</v>
       </c>
       <c r="R27" t="n">
-        <v>6687839</v>
+        <v>6687885</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300054</v>
+        <v>130299399</v>
       </c>
       <c r="B28" t="n">
-        <v>97217</v>
+        <v>81206</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490743</v>
+        <v>490680</v>
       </c>
       <c r="R28" t="n">
-        <v>6687908</v>
+        <v>6687839</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,7 +3654,7 @@
         <v>130300987</v>
       </c>
       <c r="B29" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>130299432</v>
       </c>
       <c r="B30" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,45 +3875,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130300532</v>
       </c>
       <c r="B31" t="n">
-        <v>98971</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490688</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687940</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3945,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3955,7 +3960,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,10 +3992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299120</v>
+        <v>130298471</v>
       </c>
       <c r="B32" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4017,10 +4027,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490690</v>
+        <v>490854</v>
       </c>
       <c r="R32" t="n">
-        <v>6687921</v>
+        <v>6687846</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4052,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4062,7 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,7 +4102,7 @@
         <v>130299915</v>
       </c>
       <c r="B33" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4199,7 +4209,7 @@
         <v>130299013</v>
       </c>
       <c r="B34" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4322,50 +4332,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300532</v>
+        <v>130299120</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>98974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490688</v>
+        <v>490690</v>
       </c>
       <c r="R35" t="n">
-        <v>6687940</v>
+        <v>6687921</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4397,7 +4402,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4407,12 +4412,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,7 +4442,7 @@
         <v>130298800</v>
       </c>
       <c r="B36" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130300089</v>
+        <v>130299047</v>
       </c>
       <c r="B37" t="n">
-        <v>97217</v>
+        <v>98974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490754</v>
+        <v>490706</v>
       </c>
       <c r="R37" t="n">
-        <v>6687921</v>
+        <v>6687897</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300845</v>
+        <v>130299645</v>
       </c>
       <c r="B38" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4684,14 +4684,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490638</v>
+        <v>490670</v>
       </c>
       <c r="R38" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300674</v>
+        <v>130300845</v>
       </c>
       <c r="B39" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490640</v>
+        <v>490638</v>
       </c>
       <c r="R39" t="n">
-        <v>6687937</v>
+        <v>6687897</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300601</v>
+        <v>130300674</v>
       </c>
       <c r="B40" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490648</v>
+        <v>490640</v>
       </c>
       <c r="R40" t="n">
-        <v>6687935</v>
+        <v>6687937</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,45 +4974,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130298958</v>
+        <v>130300601</v>
       </c>
       <c r="B41" t="n">
-        <v>97217</v>
+        <v>98974</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490730</v>
+        <v>490648</v>
       </c>
       <c r="R41" t="n">
-        <v>6687864</v>
+        <v>6687935</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130299645</v>
+        <v>130300089</v>
       </c>
       <c r="B42" t="n">
-        <v>98971</v>
+        <v>97220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490670</v>
+        <v>490754</v>
       </c>
       <c r="R42" t="n">
-        <v>6687843</v>
+        <v>6687921</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B43" t="n">
-        <v>98971</v>
+        <v>97220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R43" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,7 +5298,7 @@
         <v>130299124</v>
       </c>
       <c r="B44" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130299949</v>
+        <v>130298757</v>
       </c>
       <c r="B45" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490740</v>
+        <v>490809</v>
       </c>
       <c r="R45" t="n">
-        <v>6687892</v>
+        <v>6687859</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5519,10 +5519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298688</v>
+        <v>130299949</v>
       </c>
       <c r="B46" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5547,31 +5547,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490823</v>
+        <v>490740</v>
       </c>
       <c r="R46" t="n">
-        <v>6687809</v>
+        <v>6687892</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5603,7 +5589,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5613,12 +5599,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,10 +5626,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130298757</v>
+        <v>130298688</v>
       </c>
       <c r="B47" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5673,17 +5654,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490809</v>
+        <v>490823</v>
       </c>
       <c r="R47" t="n">
-        <v>6687859</v>
+        <v>6687809</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5715,7 +5710,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5725,7 +5720,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,45 +5752,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130300215</v>
+        <v>130299101</v>
       </c>
       <c r="B48" t="n">
-        <v>98971</v>
+        <v>57861</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490750</v>
+        <v>490685</v>
       </c>
       <c r="R48" t="n">
-        <v>6687940</v>
+        <v>6687923</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5832,7 +5837,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,10 +5864,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299101</v>
+        <v>130299179</v>
       </c>
       <c r="B49" t="n">
-        <v>57860</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,16 +5875,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5899,10 +5904,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490685</v>
+        <v>490663</v>
       </c>
       <c r="R49" t="n">
-        <v>6687923</v>
+        <v>6687895</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5934,7 +5939,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5944,7 +5949,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5971,50 +5981,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130299179</v>
+        <v>130300215</v>
       </c>
       <c r="B50" t="n">
-        <v>57863</v>
+        <v>98974</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490663</v>
+        <v>490750</v>
       </c>
       <c r="R50" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6046,7 +6051,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6056,12 +6061,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6088,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130298812</v>
+        <v>130299662</v>
       </c>
       <c r="B51" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,31 +6116,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490761</v>
+        <v>490664</v>
       </c>
       <c r="R51" t="n">
-        <v>6687895</v>
+        <v>6687847</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6172,7 +6158,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6182,12 +6168,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130299662</v>
+        <v>130298812</v>
       </c>
       <c r="B52" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6242,17 +6223,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490664</v>
+        <v>490761</v>
       </c>
       <c r="R52" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6279,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6289,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6324,7 +6324,7 @@
         <v>130299966</v>
       </c>
       <c r="B53" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>130298795</v>
       </c>
       <c r="B54" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>130298464</v>
       </c>
       <c r="B55" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6642,54 +6642,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299604</v>
+        <v>130300918</v>
       </c>
       <c r="B56" t="n">
-        <v>93061</v>
+        <v>97220</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490666</v>
+        <v>490628</v>
       </c>
       <c r="R56" t="n">
-        <v>6687830</v>
+        <v>6687894</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6721,7 +6712,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6731,7 +6722,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6761,7 +6752,7 @@
         <v>130299909</v>
       </c>
       <c r="B57" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6865,45 +6856,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130299604</v>
       </c>
       <c r="B58" t="n">
-        <v>97217</v>
+        <v>93062</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490666</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687830</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,47 +6972,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130298364</v>
+        <v>130299999</v>
       </c>
       <c r="B59" t="n">
-        <v>98971</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7021,10 +7012,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490775</v>
+        <v>490742</v>
       </c>
       <c r="R59" t="n">
-        <v>6687939</v>
+        <v>6687893</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7056,7 +7047,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7066,7 +7057,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7093,10 +7084,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130299214</v>
+        <v>130298364</v>
       </c>
       <c r="B60" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7121,17 +7112,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490665</v>
+        <v>490775</v>
       </c>
       <c r="R60" t="n">
-        <v>6687861</v>
+        <v>6687939</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7163,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7173,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7200,50 +7205,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299999</v>
+        <v>130299214</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>98974</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490742</v>
+        <v>490665</v>
       </c>
       <c r="R61" t="n">
-        <v>6687893</v>
+        <v>6687861</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130298671</v>
+        <v>130299512</v>
       </c>
       <c r="B2" t="n">
-        <v>98974</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490825</v>
+        <v>490708</v>
       </c>
       <c r="R2" t="n">
-        <v>6687809</v>
+        <v>6687780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130299512</v>
+        <v>130298671</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>98974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490708</v>
+        <v>490825</v>
       </c>
       <c r="R3" t="n">
-        <v>6687780</v>
+        <v>6687809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300120</v>
+        <v>130298856</v>
       </c>
       <c r="B8" t="n">
         <v>98974</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490773</v>
+        <v>490770</v>
       </c>
       <c r="R8" t="n">
-        <v>6687906</v>
+        <v>6687828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298856</v>
+        <v>130298552</v>
       </c>
       <c r="B9" t="n">
         <v>98974</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490770</v>
+        <v>490897</v>
       </c>
       <c r="R9" t="n">
-        <v>6687828</v>
+        <v>6687798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130298552</v>
+        <v>130300120</v>
       </c>
       <c r="B10" t="n">
         <v>98974</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490897</v>
+        <v>490773</v>
       </c>
       <c r="R10" t="n">
-        <v>6687798</v>
+        <v>6687906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130300768</v>
+        <v>130299757</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490629</v>
+        <v>490654</v>
       </c>
       <c r="R13" t="n">
-        <v>6687910</v>
+        <v>6687872</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130299757</v>
+        <v>130298405</v>
       </c>
       <c r="B14" t="n">
         <v>98974</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490654</v>
+        <v>490825</v>
       </c>
       <c r="R14" t="n">
-        <v>6687872</v>
+        <v>6687878</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298405</v>
+        <v>130298782</v>
       </c>
       <c r="B15" t="n">
         <v>98974</v>
@@ -2114,17 +2109,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490825</v>
+        <v>490803</v>
       </c>
       <c r="R15" t="n">
-        <v>6687878</v>
+        <v>6687883</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,59 +2202,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298782</v>
+        <v>130300768</v>
       </c>
       <c r="B16" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490803</v>
+        <v>490629</v>
       </c>
       <c r="R16" t="n">
-        <v>6687883</v>
+        <v>6687910</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,32 +2314,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130299411</v>
+        <v>130298439</v>
       </c>
       <c r="B17" t="n">
-        <v>98974</v>
+        <v>92074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490679</v>
+        <v>490826</v>
       </c>
       <c r="R17" t="n">
-        <v>6687837</v>
+        <v>6687871</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298439</v>
+        <v>130299411</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>98974</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490826</v>
+        <v>490679</v>
       </c>
       <c r="R18" t="n">
-        <v>6687871</v>
+        <v>6687837</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,50 +2528,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299657</v>
+        <v>130299218</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490669</v>
+        <v>490666</v>
       </c>
       <c r="R19" t="n">
-        <v>6687844</v>
+        <v>6687855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inte långt bort.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130299218</v>
+        <v>130298529</v>
       </c>
       <c r="B20" t="n">
         <v>98974</v>
@@ -2673,17 +2663,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490666</v>
+        <v>490885</v>
       </c>
       <c r="R20" t="n">
-        <v>6687855</v>
+        <v>6687821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,47 +2877,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130298529</v>
+        <v>130299657</v>
       </c>
       <c r="B22" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490885</v>
+        <v>490669</v>
       </c>
       <c r="R22" t="n">
-        <v>6687821</v>
+        <v>6687844</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,7 +2952,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2967,7 +2962,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130298467</v>
+        <v>130300938</v>
       </c>
       <c r="B23" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490855</v>
+        <v>490629</v>
       </c>
       <c r="R23" t="n">
-        <v>6687847</v>
+        <v>6687895</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,7 +3074,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,50 +3106,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130300626</v>
+        <v>130298467</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>98974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490855</v>
       </c>
       <c r="R24" t="n">
-        <v>6687936</v>
+        <v>6687847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3186,12 +3186,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300938</v>
+        <v>130300626</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,16 +3224,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3247,16 +3242,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490629</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>6687895</v>
+        <v>6687936</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Födosök.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300054</v>
+        <v>130298421</v>
       </c>
       <c r="B26" t="n">
-        <v>97220</v>
+        <v>91776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490743</v>
+        <v>490831</v>
       </c>
       <c r="R26" t="n">
-        <v>6687908</v>
+        <v>6687885</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130298421</v>
+        <v>130299399</v>
       </c>
       <c r="B27" t="n">
-        <v>91776</v>
+        <v>81206</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490831</v>
+        <v>490680</v>
       </c>
       <c r="R27" t="n">
-        <v>6687885</v>
+        <v>6687839</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130299399</v>
+        <v>130300054</v>
       </c>
       <c r="B28" t="n">
-        <v>81206</v>
+        <v>97220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490680</v>
+        <v>490743</v>
       </c>
       <c r="R28" t="n">
-        <v>6687839</v>
+        <v>6687908</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,38 +3651,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300987</v>
+        <v>130300532</v>
       </c>
       <c r="B29" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490657</v>
+        <v>490688</v>
       </c>
       <c r="R29" t="n">
-        <v>6687863</v>
+        <v>6687940</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,7 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,50 +3880,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130300532</v>
+        <v>130298471</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>98974</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490688</v>
+        <v>490854</v>
       </c>
       <c r="R31" t="n">
-        <v>6687940</v>
+        <v>6687846</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,12 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,7 +3987,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130298471</v>
+        <v>130299120</v>
       </c>
       <c r="B32" t="n">
         <v>98974</v>
@@ -4027,10 +4022,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490854</v>
+        <v>490690</v>
       </c>
       <c r="R32" t="n">
-        <v>6687846</v>
+        <v>6687921</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,45 +4327,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130299120</v>
+        <v>130300987</v>
       </c>
       <c r="B35" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490690</v>
+        <v>490657</v>
       </c>
       <c r="R35" t="n">
-        <v>6687921</v>
+        <v>6687863</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130299047</v>
+        <v>130298958</v>
       </c>
       <c r="B37" t="n">
-        <v>98974</v>
+        <v>97220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490706</v>
+        <v>490730</v>
       </c>
       <c r="R37" t="n">
-        <v>6687897</v>
+        <v>6687864</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,32 +4653,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130299645</v>
+        <v>130300089</v>
       </c>
       <c r="B38" t="n">
-        <v>98974</v>
+        <v>97220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490670</v>
+        <v>490754</v>
       </c>
       <c r="R38" t="n">
-        <v>6687843</v>
+        <v>6687921</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130300845</v>
+        <v>130299645</v>
       </c>
       <c r="B39" t="n">
         <v>98974</v>
@@ -4791,14 +4791,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490638</v>
+        <v>490670</v>
       </c>
       <c r="R39" t="n">
-        <v>6687897</v>
+        <v>6687843</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130300674</v>
+        <v>130299047</v>
       </c>
       <c r="B40" t="n">
         <v>98974</v>
@@ -4898,14 +4898,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490640</v>
+        <v>490706</v>
       </c>
       <c r="R40" t="n">
-        <v>6687937</v>
+        <v>6687897</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300601</v>
+        <v>130300845</v>
       </c>
       <c r="B41" t="n">
         <v>98974</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490648</v>
+        <v>490638</v>
       </c>
       <c r="R41" t="n">
-        <v>6687935</v>
+        <v>6687897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,45 +5081,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300089</v>
+        <v>130300674</v>
       </c>
       <c r="B42" t="n">
-        <v>97220</v>
+        <v>98974</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490754</v>
+        <v>490640</v>
       </c>
       <c r="R42" t="n">
-        <v>6687921</v>
+        <v>6687937</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,45 +5188,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130298958</v>
+        <v>130300601</v>
       </c>
       <c r="B43" t="n">
-        <v>97220</v>
+        <v>98974</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490730</v>
+        <v>490648</v>
       </c>
       <c r="R43" t="n">
-        <v>6687864</v>
+        <v>6687935</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,50 +5295,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299124</v>
+        <v>130299949</v>
       </c>
       <c r="B44" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490689</v>
+        <v>490740</v>
       </c>
       <c r="R44" t="n">
-        <v>6687918</v>
+        <v>6687892</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5370,7 +5365,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5380,12 +5375,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,7 +5402,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130298757</v>
+        <v>130298688</v>
       </c>
       <c r="B45" t="n">
         <v>98974</v>
@@ -5440,17 +5430,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490809</v>
+        <v>490823</v>
       </c>
       <c r="R45" t="n">
-        <v>6687859</v>
+        <v>6687809</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5482,7 +5486,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5492,7 +5496,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5519,7 +5528,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130299949</v>
+        <v>130298757</v>
       </c>
       <c r="B46" t="n">
         <v>98974</v>
@@ -5554,10 +5563,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490740</v>
+        <v>490809</v>
       </c>
       <c r="R46" t="n">
-        <v>6687892</v>
+        <v>6687859</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5589,7 +5598,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5599,7 +5608,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5626,47 +5635,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130298688</v>
+        <v>130299124</v>
       </c>
       <c r="B47" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490823</v>
+        <v>490689</v>
       </c>
       <c r="R47" t="n">
-        <v>6687809</v>
+        <v>6687918</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5981,7 +5981,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130300215</v>
+        <v>130298812</v>
       </c>
       <c r="B50" t="n">
         <v>98974</v>
@@ -6009,17 +6009,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490750</v>
+        <v>490761</v>
       </c>
       <c r="R50" t="n">
-        <v>6687940</v>
+        <v>6687895</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6051,7 +6065,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6061,7 +6075,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,7 +6214,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130298812</v>
+        <v>130300215</v>
       </c>
       <c r="B52" t="n">
         <v>98974</v>
@@ -6223,31 +6242,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490761</v>
+        <v>490750</v>
       </c>
       <c r="R52" t="n">
-        <v>6687895</v>
+        <v>6687940</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6279,7 +6284,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6289,12 +6294,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6642,45 +6642,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130300918</v>
+        <v>130299604</v>
       </c>
       <c r="B56" t="n">
-        <v>97220</v>
+        <v>93062</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490628</v>
+        <v>490666</v>
       </c>
       <c r="R56" t="n">
-        <v>6687894</v>
+        <v>6687830</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6712,7 +6721,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6722,7 +6731,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6856,54 +6865,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130299604</v>
+        <v>130300918</v>
       </c>
       <c r="B58" t="n">
-        <v>93062</v>
+        <v>97220</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490666</v>
+        <v>490628</v>
       </c>
       <c r="R58" t="n">
-        <v>6687830</v>
+        <v>6687894</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 57804-2025 artfynd.xlsx
+++ b/artfynd/A 57804-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130299512</v>
+        <v>130298958</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490708</v>
+        <v>490730</v>
       </c>
       <c r="R2" t="n">
-        <v>6687780</v>
+        <v>6687864</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130298671</v>
+        <v>130299909</v>
       </c>
       <c r="B3" t="n">
-        <v>98974</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490825</v>
+        <v>490723</v>
       </c>
       <c r="R3" t="n">
-        <v>6687809</v>
+        <v>6687910</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300998</v>
+        <v>130299966</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490659</v>
+        <v>490741</v>
       </c>
       <c r="R4" t="n">
-        <v>6687865</v>
+        <v>6687894</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130300930</v>
+        <v>130300054</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490628</v>
+        <v>490743</v>
       </c>
       <c r="R5" t="n">
-        <v>6687894</v>
+        <v>6687908</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300146</v>
+        <v>130300089</v>
       </c>
       <c r="B6" t="n">
-        <v>98974</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490771</v>
+        <v>490754</v>
       </c>
       <c r="R6" t="n">
-        <v>6687913</v>
+        <v>6687921</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,45 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130299032</v>
+        <v>130300918</v>
       </c>
       <c r="B7" t="n">
-        <v>98974</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490723</v>
+        <v>490628</v>
       </c>
       <c r="R7" t="n">
-        <v>6687899</v>
+        <v>6687894</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130298856</v>
+        <v>130298439</v>
       </c>
       <c r="B8" t="n">
-        <v>98974</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490770</v>
+        <v>490826</v>
       </c>
       <c r="R8" t="n">
-        <v>6687828</v>
+        <v>6687871</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130298552</v>
+        <v>130299399</v>
       </c>
       <c r="B9" t="n">
-        <v>98974</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490897</v>
+        <v>490680</v>
       </c>
       <c r="R9" t="n">
-        <v>6687798</v>
+        <v>6687839</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300120</v>
+        <v>130298421</v>
       </c>
       <c r="B10" t="n">
-        <v>98974</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490773</v>
+        <v>490831</v>
       </c>
       <c r="R10" t="n">
-        <v>6687906</v>
+        <v>6687885</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130299228</v>
+        <v>130298423</v>
       </c>
       <c r="B11" t="n">
-        <v>98974</v>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490669</v>
+        <v>490832</v>
       </c>
       <c r="R11" t="n">
-        <v>6687842</v>
+        <v>6687879</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,45 +1745,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130298423</v>
+        <v>130299604</v>
       </c>
       <c r="B12" t="n">
-        <v>92235</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490832</v>
+        <v>490666</v>
       </c>
       <c r="R12" t="n">
-        <v>6687879</v>
+        <v>6687830</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,45 +1861,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130299757</v>
+        <v>130299101</v>
       </c>
       <c r="B13" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490654</v>
+        <v>490685</v>
       </c>
       <c r="R13" t="n">
-        <v>6687872</v>
+        <v>6687923</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt över större yta.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,45 +1973,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130298405</v>
+        <v>130299124</v>
       </c>
       <c r="B14" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490825</v>
+        <v>490689</v>
       </c>
       <c r="R14" t="n">
-        <v>6687878</v>
+        <v>6687918</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2058,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I närheten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,47 +2090,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298782</v>
+        <v>130299432</v>
       </c>
       <c r="B15" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490803</v>
+        <v>490697</v>
       </c>
       <c r="R15" t="n">
-        <v>6687883</v>
+        <v>6687828</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,14 +2202,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300768</v>
+        <v>130299657</v>
       </c>
       <c r="B16" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2233,19 +2233,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490669</v>
       </c>
       <c r="R16" t="n">
-        <v>6687910</v>
+        <v>6687844</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Inte långt bort.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,45 +2319,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130298439</v>
+        <v>130300768</v>
       </c>
       <c r="B17" t="n">
-        <v>92074</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490826</v>
+        <v>490629</v>
       </c>
       <c r="R17" t="n">
-        <v>6687871</v>
+        <v>6687910</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2404,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,45 +2431,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130299411</v>
+        <v>130300938</v>
       </c>
       <c r="B18" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490679</v>
+        <v>490629</v>
       </c>
       <c r="R18" t="n">
-        <v>6687837</v>
+        <v>6687895</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2511,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,45 +2543,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130299218</v>
+        <v>130300987</v>
       </c>
       <c r="B19" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490666</v>
+        <v>490657</v>
       </c>
       <c r="R19" t="n">
-        <v>6687855</v>
+        <v>6687863</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,7 +2618,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2628,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,47 +2655,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298529</v>
+        <v>130299179</v>
       </c>
       <c r="B20" t="n">
-        <v>98974</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2684,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490885</v>
+        <v>490663</v>
       </c>
       <c r="R20" t="n">
-        <v>6687821</v>
+        <v>6687895</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2740,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,47 +2772,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298375</v>
+        <v>130299512</v>
       </c>
       <c r="B21" t="n">
-        <v>98974</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490816</v>
+        <v>490708</v>
       </c>
       <c r="R21" t="n">
-        <v>6687911</v>
+        <v>6687780</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,7 +2847,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2857,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130299657</v>
+        <v>130300626</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,16 +2900,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2908,19 +2920,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490669</v>
+        <v>490648</v>
       </c>
       <c r="R22" t="n">
-        <v>6687844</v>
+        <v>6687936</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2952,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2974,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Inte långt bort.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,45 +3006,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130300938</v>
+        <v>130299999</v>
       </c>
       <c r="B23" t="n">
-        <v>57861</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490629</v>
+        <v>490742</v>
       </c>
       <c r="R23" t="n">
-        <v>6687895</v>
+        <v>6687893</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3074,12 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosök.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,45 +3118,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130298467</v>
+        <v>130300532</v>
       </c>
       <c r="B24" t="n">
-        <v>98974</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490855</v>
+        <v>490688</v>
       </c>
       <c r="R24" t="n">
-        <v>6687847</v>
+        <v>6687940</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3176,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3186,7 +3203,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Urholkad märg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,50 +3235,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300626</v>
+        <v>130298364</v>
       </c>
       <c r="B25" t="n">
-        <v>57864</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490775</v>
       </c>
       <c r="R25" t="n">
-        <v>6687936</v>
+        <v>6687939</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3288,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3298,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,45 +3356,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130298421</v>
+        <v>130298375</v>
       </c>
       <c r="B26" t="n">
-        <v>91776</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490831</v>
+        <v>490816</v>
       </c>
       <c r="R26" t="n">
-        <v>6687885</v>
+        <v>6687911</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3440,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3450,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,32 +3477,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130299399</v>
+        <v>130298405</v>
       </c>
       <c r="B27" t="n">
-        <v>81206</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490680</v>
+        <v>490825</v>
       </c>
       <c r="R27" t="n">
-        <v>6687839</v>
+        <v>6687878</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3507,7 +3547,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3557,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,32 +3584,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300054</v>
+        <v>130298464</v>
       </c>
       <c r="B28" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490743</v>
+        <v>490854</v>
       </c>
       <c r="R28" t="n">
-        <v>6687908</v>
+        <v>6687851</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3654,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3664,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,50 +3691,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300532</v>
+        <v>130298467</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490688</v>
+        <v>490855</v>
       </c>
       <c r="R29" t="n">
-        <v>6687940</v>
+        <v>6687847</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3761,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3771,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Urholkad märg.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,50 +3798,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130299432</v>
+        <v>130298471</v>
       </c>
       <c r="B30" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490697</v>
+        <v>490854</v>
       </c>
       <c r="R30" t="n">
-        <v>6687828</v>
+        <v>6687846</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3843,7 +3868,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,7 +3878,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,10 +3905,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130298471</v>
+        <v>130298529</v>
       </c>
       <c r="B31" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,17 +3933,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490854</v>
+        <v>490885</v>
       </c>
       <c r="R31" t="n">
-        <v>6687846</v>
+        <v>6687821</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3950,7 +3989,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3999,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130299120</v>
+        <v>130298552</v>
       </c>
       <c r="B32" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490690</v>
+        <v>490897</v>
       </c>
       <c r="R32" t="n">
-        <v>6687921</v>
+        <v>6687798</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4057,7 +4096,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,7 +4106,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130299915</v>
+        <v>130298617</v>
       </c>
       <c r="B33" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490724</v>
+        <v>490911</v>
       </c>
       <c r="R33" t="n">
-        <v>6687908</v>
+        <v>6687779</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4164,7 +4203,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4174,7 +4213,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4201,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130299013</v>
+        <v>130298671</v>
       </c>
       <c r="B34" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,31 +4268,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490722</v>
+        <v>490825</v>
       </c>
       <c r="R34" t="n">
-        <v>6687888</v>
+        <v>6687809</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4285,7 +4310,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,12 +4320,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt över ytan, några överblommade.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4327,38 +4347,47 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300987</v>
+        <v>130298688</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4367,10 +4396,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490657</v>
+        <v>490823</v>
       </c>
       <c r="R35" t="n">
-        <v>6687863</v>
+        <v>6687809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4402,7 +4431,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4412,7 +4441,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 100 bladrosetter, några överblommade.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,10 +4473,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130298800</v>
+        <v>130298757</v>
       </c>
       <c r="B36" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490768</v>
+        <v>490809</v>
       </c>
       <c r="R36" t="n">
-        <v>6687895</v>
+        <v>6687859</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4509,7 +4543,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4519,7 +4553,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,45 +4580,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130298958</v>
+        <v>130298782</v>
       </c>
       <c r="B37" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490730</v>
+        <v>490803</v>
       </c>
       <c r="R37" t="n">
-        <v>6687864</v>
+        <v>6687883</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4616,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4626,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,32 +4701,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130300089</v>
+        <v>130298795</v>
       </c>
       <c r="B38" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4688,10 +4736,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490754</v>
+        <v>490776</v>
       </c>
       <c r="R38" t="n">
-        <v>6687921</v>
+        <v>6687899</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,7 +4771,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,7 +4781,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,10 +4808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130299645</v>
+        <v>130298800</v>
       </c>
       <c r="B39" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,10 +4843,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490670</v>
+        <v>490768</v>
       </c>
       <c r="R39" t="n">
-        <v>6687843</v>
+        <v>6687895</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4830,7 +4878,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,7 +4888,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,10 +4915,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130299047</v>
+        <v>130298812</v>
       </c>
       <c r="B40" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,17 +4943,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490706</v>
+        <v>490761</v>
       </c>
       <c r="R40" t="n">
-        <v>6687897</v>
+        <v>6687895</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4937,7 +4999,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +5009,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 100.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,10 +5041,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130300845</v>
+        <v>130298856</v>
       </c>
       <c r="B41" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5005,14 +5072,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490638</v>
+        <v>490770</v>
       </c>
       <c r="R41" t="n">
-        <v>6687897</v>
+        <v>6687828</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5044,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5054,7 +5121,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5148,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130300674</v>
+        <v>130299013</v>
       </c>
       <c r="B42" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5109,17 +5176,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490640</v>
+        <v>490722</v>
       </c>
       <c r="R42" t="n">
-        <v>6687937</v>
+        <v>6687888</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5151,7 +5232,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5161,7 +5242,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt över ytan, några överblommade.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130300601</v>
+        <v>130299032</v>
       </c>
       <c r="B43" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,14 +5305,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490648</v>
+        <v>490723</v>
       </c>
       <c r="R43" t="n">
-        <v>6687935</v>
+        <v>6687899</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5258,7 +5344,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5268,7 +5354,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,10 +5381,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130299949</v>
+        <v>130299047</v>
       </c>
       <c r="B44" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5330,10 +5416,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490740</v>
+        <v>490706</v>
       </c>
       <c r="R44" t="n">
-        <v>6687892</v>
+        <v>6687897</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5365,7 +5451,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5375,7 +5461,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,10 +5488,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130298688</v>
+        <v>130299120</v>
       </c>
       <c r="B45" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5430,31 +5516,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490823</v>
+        <v>490690</v>
       </c>
       <c r="R45" t="n">
-        <v>6687809</v>
+        <v>6687921</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5486,7 +5558,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5496,12 +5568,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 100 bladrosetter, några överblommade.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5528,10 +5595,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130298757</v>
+        <v>130299214</v>
       </c>
       <c r="B46" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5563,10 +5630,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490809</v>
+        <v>490665</v>
       </c>
       <c r="R46" t="n">
-        <v>6687859</v>
+        <v>6687861</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5598,7 +5665,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5608,7 +5675,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5635,50 +5702,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130299124</v>
+        <v>130299218</v>
       </c>
       <c r="B47" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490689</v>
+        <v>490666</v>
       </c>
       <c r="R47" t="n">
-        <v>6687918</v>
+        <v>6687855</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5710,7 +5772,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5720,12 +5782,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I närheten.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,50 +5809,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130299101</v>
+        <v>130299228</v>
       </c>
       <c r="B48" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490685</v>
+        <v>490669</v>
       </c>
       <c r="R48" t="n">
-        <v>6687923</v>
+        <v>6687842</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5827,7 +5879,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5837,7 +5889,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5864,50 +5916,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130299179</v>
+        <v>130299411</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490663</v>
+        <v>490679</v>
       </c>
       <c r="R49" t="n">
-        <v>6687895</v>
+        <v>6687837</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5939,7 +5986,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5949,12 +5996,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,10 +6023,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130298812</v>
+        <v>130299645</v>
       </c>
       <c r="B50" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,31 +6051,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490761</v>
+        <v>490670</v>
       </c>
       <c r="R50" t="n">
-        <v>6687895</v>
+        <v>6687843</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6093,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6075,12 +6103,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 100.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6133,7 @@
         <v>130299662</v>
       </c>
       <c r="B51" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6214,10 +6237,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130300215</v>
+        <v>130299757</v>
       </c>
       <c r="B52" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,10 +6272,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490750</v>
+        <v>490654</v>
       </c>
       <c r="R52" t="n">
-        <v>6687940</v>
+        <v>6687872</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6284,7 +6307,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6294,7 +6317,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt över större yta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6321,32 +6349,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130299966</v>
+        <v>130299915</v>
       </c>
       <c r="B53" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6356,10 +6384,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490741</v>
+        <v>490724</v>
       </c>
       <c r="R53" t="n">
-        <v>6687894</v>
+        <v>6687908</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,7 +6419,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6401,7 +6429,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6428,10 +6456,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130298795</v>
+        <v>130299949</v>
       </c>
       <c r="B54" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6463,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490776</v>
+        <v>490740</v>
       </c>
       <c r="R54" t="n">
-        <v>6687899</v>
+        <v>6687892</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6498,7 +6526,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6508,7 +6536,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,10 +6563,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130298464</v>
+        <v>130300120</v>
       </c>
       <c r="B55" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6570,10 +6598,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490854</v>
+        <v>490773</v>
       </c>
       <c r="R55" t="n">
-        <v>6687851</v>
+        <v>6687906</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6605,7 +6633,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,7 +6643,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6642,54 +6670,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130299604</v>
+        <v>130300146</v>
       </c>
       <c r="B56" t="n">
-        <v>93062</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sultentjärnen, Sultentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490666</v>
+        <v>490771</v>
       </c>
       <c r="R56" t="n">
-        <v>6687830</v>
+        <v>6687913</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6721,7 +6740,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6731,7 +6750,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6758,32 +6777,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130299909</v>
+        <v>130300215</v>
       </c>
       <c r="B57" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6793,10 +6812,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490723</v>
+        <v>490750</v>
       </c>
       <c r="R57" t="n">
-        <v>6687910</v>
+        <v>6687940</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6828,7 +6847,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6838,7 +6857,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6865,32 +6884,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130300918</v>
+        <v>130300601</v>
       </c>
       <c r="B58" t="n">
-        <v>97220</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6900,10 +6919,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490628</v>
+        <v>490648</v>
       </c>
       <c r="R58" t="n">
-        <v>6687894</v>
+        <v>6687935</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6935,7 +6954,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6945,7 +6964,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,50 +6991,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130299999</v>
+        <v>130300674</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490742</v>
+        <v>490640</v>
       </c>
       <c r="R59" t="n">
-        <v>6687893</v>
+        <v>6687937</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7047,7 +7061,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7057,7 +7071,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,10 +7098,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130298364</v>
+        <v>130300845</v>
       </c>
       <c r="B60" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7112,31 +7126,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490775</v>
+        <v>490638</v>
       </c>
       <c r="R60" t="n">
-        <v>6687939</v>
+        <v>6687897</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,10 +7205,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130299214</v>
+        <v>130300930</v>
       </c>
       <c r="B61" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,14 +7236,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490665</v>
+        <v>490628</v>
       </c>
       <c r="R61" t="n">
-        <v>6687861</v>
+        <v>6687894</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7309,6 +7309,113 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130300998</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sultentjärnen, Sultentjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490659</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6687865</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
